--- a/games_database.xlsx
+++ b/games_database.xlsx
@@ -8,21 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\JustAnotherDiscordRichPresenceApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D729FC-C015-49C9-8F83-8B4D7ACBE462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDA660D-5856-4240-8724-10ECF210600F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="PS3" sheetId="1" r:id="rId1"/>
-    <sheet name="PS4" sheetId="2" r:id="rId2"/>
-    <sheet name="PS5" sheetId="3" r:id="rId3"/>
+    <sheet name="OG Xbox" sheetId="7" r:id="rId1"/>
+    <sheet name="Xbox 360" sheetId="6" r:id="rId2"/>
+    <sheet name="Xbox Series X" sheetId="8" r:id="rId3"/>
+    <sheet name="Nintendo Switch" sheetId="9" r:id="rId4"/>
+    <sheet name="PS1" sheetId="5" r:id="rId5"/>
+    <sheet name="PS2" sheetId="4" r:id="rId6"/>
+    <sheet name="PS3" sheetId="1" r:id="rId7"/>
+    <sheet name="PS4" sheetId="2" r:id="rId8"/>
+    <sheet name="PS5" sheetId="3" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="957">
   <si>
     <t>Game Title</t>
   </si>
@@ -117,9 +123,6 @@
     <t>Ready</t>
   </si>
   <si>
-    <t>Demon's Souls</t>
-  </si>
-  <si>
     <t>Playing Demon's Souls</t>
   </si>
   <si>
@@ -2875,13 +2878,34 @@
   </si>
   <si>
     <t>PS5 Game 55 Cover</t>
+  </si>
+  <si>
+    <t>https://cdn-icons-png.flaticon.com/512/1/1443.png</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn3.gstatic.com/images?q=tbn:ANd9GcR5s3ksnAtcuzodevtQ7mG36TyDHu42wPcQ2SzE-7MSMmKZyYFc</t>
+  </si>
+  <si>
+    <t>Demon's Souls (Originial PS3)</t>
+  </si>
+  <si>
+    <t>Xenosaga Episode I – Der Wille zur Macht</t>
+  </si>
+  <si>
+    <t>Playing Xenosaga Episode I – Der Wille zur Macht</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/6/6b/Xenosaga1box.jpg</t>
+  </si>
+  <si>
+    <t>Xenosaga Episode I – Der Wille zur Macht Cover</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2893,6 +2917,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2927,16 +2959,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3236,6 +3271,243 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2AB5DEB-13B6-423C-9110-A18F97C06ED2}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C17BA24-4C1D-4125-9B28-FC742EBF1548}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5735029B-8832-4349-8F35-DCD2756C465B}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C4B4D7-56FC-4BEC-AD8F-23A2F4F51983}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFEDB219-5142-4DD7-A4D0-88AB6C946699}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97AAA216-E55B-4412-AC18-BF6E7B0E759E}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>953</v>
+      </c>
+      <c r="B2" t="s">
+        <v>954</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="E2" t="s">
+        <v>956</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{FC7B53FC-2FC4-4620-9927-238AB6CDCE35}"/>
+    <hyperlink ref="D2" r:id="rId2" xr:uid="{1D63B975-747D-47E3-909F-94B9AAED4962}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3243,9 +3515,9 @@
     <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="102.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3288,8 +3560,8 @@
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
-        <v>12</v>
+      <c r="F2" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -3311,8 +3583,8 @@
       <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
-        <v>12</v>
+      <c r="F3" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -3334,8 +3606,8 @@
       <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
-        <v>12</v>
+      <c r="F4" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G4" t="s">
         <v>24</v>
@@ -3351,14 +3623,14 @@
       <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
-        <v>27</v>
+      <c r="D5" s="2" t="s">
+        <v>951</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
       </c>
-      <c r="F5" t="s">
-        <v>29</v>
+      <c r="F5" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
@@ -3366,22 +3638,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>952</v>
+      </c>
+      <c r="B6" t="s">
         <v>31</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
         <v>33</v>
       </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
+      <c r="F6" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
@@ -3389,137 +3661,137 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
         <v>36</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
       </c>
       <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
         <v>38</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="G7" t="s">
         <v>39</v>
-      </c>
-      <c r="F7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
         <v>41</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>43</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>44</v>
       </c>
-      <c r="E8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" t="s">
-        <v>29</v>
+      <c r="F8" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
         <v>46</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
         <v>48</v>
       </c>
-      <c r="E9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" t="s">
-        <v>29</v>
+      <c r="F9" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
         <v>50</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>52</v>
       </c>
-      <c r="E10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
+      <c r="F10" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
         <v>54</v>
-      </c>
-      <c r="B11" t="s">
-        <v>55</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
         <v>56</v>
       </c>
-      <c r="E11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" t="s">
-        <v>29</v>
+      <c r="F11" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
         <v>58</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>59</v>
-      </c>
-      <c r="C12" t="s">
-        <v>60</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
+        <v>60</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -3527,10 +3799,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
         <v>62</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
@@ -3539,33 +3811,33 @@
         <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" t="s">
-        <v>35</v>
+        <v>63</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
         <v>65</v>
       </c>
-      <c r="B14" t="s">
-        <v>66</v>
-      </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" t="s">
-        <v>29</v>
+        <v>66</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -3573,22 +3845,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
         <v>68</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
       </c>
       <c r="D15" t="s">
         <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" t="s">
-        <v>29</v>
+        <v>70</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G15" t="s">
         <v>30</v>
@@ -3596,22 +3868,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" t="s">
         <v>72</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
       </c>
       <c r="C16" t="s">
         <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" t="s">
-        <v>29</v>
+        <v>73</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G16" t="s">
         <v>30</v>
@@ -3619,22 +3891,22 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" t="s">
         <v>75</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
       </c>
       <c r="C17" t="s">
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17" t="s">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G17" t="s">
         <v>30</v>
@@ -3642,22 +3914,22 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" t="s">
         <v>79</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
       </c>
       <c r="C18" t="s">
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F18" t="s">
-        <v>29</v>
+        <v>80</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -3665,22 +3937,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" t="s">
         <v>82</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" t="s">
         <v>83</v>
       </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19" t="s">
-        <v>35</v>
+      <c r="F19" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G19" t="s">
         <v>30</v>
@@ -3688,22 +3960,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" t="s">
         <v>85</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" t="s">
         <v>86</v>
       </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" t="s">
-        <v>87</v>
-      </c>
-      <c r="F20" t="s">
-        <v>35</v>
+      <c r="F20" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -3711,33 +3983,33 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
         <v>88</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" t="s">
         <v>89</v>
       </c>
-      <c r="C21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" t="s">
-        <v>90</v>
-      </c>
-      <c r="F21" t="s">
-        <v>35</v>
+      <c r="F21" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" t="s">
         <v>91</v>
-      </c>
-      <c r="B22" t="s">
-        <v>92</v>
       </c>
       <c r="C22" t="s">
         <v>16</v>
@@ -3746,10 +4018,10 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22" t="s">
-        <v>35</v>
+        <v>92</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G22" t="s">
         <v>30</v>
@@ -3757,22 +4029,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" t="s">
         <v>94</v>
       </c>
-      <c r="B23" t="s">
-        <v>95</v>
-      </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
       </c>
       <c r="E23" t="s">
-        <v>96</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
+        <v>95</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
@@ -3780,10 +4052,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" t="s">
         <v>97</v>
-      </c>
-      <c r="B24" t="s">
-        <v>98</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
@@ -3792,21 +4064,21 @@
         <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>99</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
+        <v>98</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" t="s">
         <v>100</v>
-      </c>
-      <c r="B25" t="s">
-        <v>101</v>
       </c>
       <c r="C25" t="s">
         <v>16</v>
@@ -3815,10 +4087,10 @@
         <v>27</v>
       </c>
       <c r="E25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" t="s">
-        <v>12</v>
+        <v>101</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G25" t="s">
         <v>24</v>
@@ -3826,22 +4098,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" t="s">
         <v>103</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
         <v>104</v>
       </c>
-      <c r="C26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" t="s">
-        <v>105</v>
-      </c>
-      <c r="F26" t="s">
-        <v>29</v>
+      <c r="F26" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G26" t="s">
         <v>30</v>
@@ -3849,22 +4121,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" t="s">
         <v>106</v>
-      </c>
-      <c r="B27" t="s">
-        <v>107</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E27" t="s">
-        <v>108</v>
-      </c>
-      <c r="F27" t="s">
-        <v>35</v>
+        <v>107</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G27" t="s">
         <v>30</v>
@@ -3872,22 +4144,22 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" t="s">
         <v>109</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" t="s">
         <v>110</v>
       </c>
-      <c r="C28" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" t="s">
-        <v>35</v>
+      <c r="F28" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G28" t="s">
         <v>30</v>
@@ -3895,45 +4167,45 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" t="s">
         <v>112</v>
-      </c>
-      <c r="B29" t="s">
-        <v>113</v>
       </c>
       <c r="C29" t="s">
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s">
-        <v>114</v>
-      </c>
-      <c r="F29" t="s">
-        <v>78</v>
+        <v>113</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" t="s">
         <v>115</v>
-      </c>
-      <c r="B30" t="s">
-        <v>116</v>
       </c>
       <c r="C30" t="s">
         <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E30" t="s">
-        <v>117</v>
-      </c>
-      <c r="F30" t="s">
-        <v>12</v>
+        <v>116</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
@@ -3941,33 +4213,33 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" t="s">
         <v>118</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" t="s">
         <v>119</v>
       </c>
-      <c r="C31" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31" t="s">
-        <v>120</v>
-      </c>
-      <c r="F31" t="s">
-        <v>29</v>
+      <c r="F31" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>120</v>
+      </c>
+      <c r="B32" t="s">
         <v>121</v>
-      </c>
-      <c r="B32" t="s">
-        <v>122</v>
       </c>
       <c r="C32" t="s">
         <v>21</v>
@@ -3976,10 +4248,10 @@
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>123</v>
-      </c>
-      <c r="F32" t="s">
-        <v>29</v>
+        <v>122</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G32" t="s">
         <v>24</v>
@@ -3987,10 +4259,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" t="s">
         <v>124</v>
-      </c>
-      <c r="B33" t="s">
-        <v>125</v>
       </c>
       <c r="C33" t="s">
         <v>21</v>
@@ -3999,10 +4271,10 @@
         <v>17</v>
       </c>
       <c r="E33" t="s">
-        <v>126</v>
-      </c>
-      <c r="F33" t="s">
-        <v>12</v>
+        <v>125</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G33" t="s">
         <v>30</v>
@@ -4010,10 +4282,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" t="s">
         <v>127</v>
-      </c>
-      <c r="B34" t="s">
-        <v>128</v>
       </c>
       <c r="C34" t="s">
         <v>21</v>
@@ -4022,10 +4294,10 @@
         <v>22</v>
       </c>
       <c r="E34" t="s">
-        <v>129</v>
-      </c>
-      <c r="F34" t="s">
-        <v>29</v>
+        <v>128</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G34" t="s">
         <v>30</v>
@@ -4033,10 +4305,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" t="s">
         <v>130</v>
-      </c>
-      <c r="B35" t="s">
-        <v>131</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
@@ -4045,10 +4317,10 @@
         <v>27</v>
       </c>
       <c r="E35" t="s">
-        <v>132</v>
-      </c>
-      <c r="F35" t="s">
-        <v>78</v>
+        <v>131</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G35" t="s">
         <v>30</v>
@@ -4056,22 +4328,22 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" t="s">
         <v>133</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" t="s">
         <v>134</v>
       </c>
-      <c r="C36" t="s">
-        <v>60</v>
-      </c>
-      <c r="D36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E36" t="s">
-        <v>135</v>
-      </c>
-      <c r="F36" t="s">
-        <v>29</v>
+      <c r="F36" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G36" t="s">
         <v>24</v>
@@ -4079,22 +4351,22 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>135</v>
+      </c>
+      <c r="B37" t="s">
         <v>136</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" t="s">
         <v>137</v>
       </c>
-      <c r="C37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" t="s">
-        <v>138</v>
-      </c>
-      <c r="F37" t="s">
-        <v>29</v>
+      <c r="F37" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G37" t="s">
         <v>24</v>
@@ -4102,45 +4374,45 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>138</v>
+      </c>
+      <c r="B38" t="s">
         <v>139</v>
-      </c>
-      <c r="B38" t="s">
-        <v>140</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E38" t="s">
-        <v>141</v>
-      </c>
-      <c r="F38" t="s">
-        <v>29</v>
+        <v>140</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>141</v>
+      </c>
+      <c r="B39" t="s">
         <v>142</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" t="s">
         <v>143</v>
       </c>
-      <c r="C39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" t="s">
-        <v>144</v>
-      </c>
-      <c r="F39" t="s">
-        <v>29</v>
+      <c r="F39" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G39" t="s">
         <v>24</v>
@@ -4148,22 +4420,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" t="s">
         <v>145</v>
-      </c>
-      <c r="B40" t="s">
-        <v>146</v>
       </c>
       <c r="C40" t="s">
         <v>9</v>
       </c>
       <c r="D40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E40" t="s">
-        <v>147</v>
-      </c>
-      <c r="F40" t="s">
-        <v>12</v>
+        <v>146</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G40" t="s">
         <v>13</v>
@@ -4171,45 +4443,45 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" t="s">
         <v>148</v>
-      </c>
-      <c r="B41" t="s">
-        <v>149</v>
       </c>
       <c r="C41" t="s">
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E41" t="s">
-        <v>150</v>
-      </c>
-      <c r="F41" t="s">
-        <v>12</v>
+        <v>149</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" t="s">
         <v>151</v>
       </c>
-      <c r="B42" t="s">
-        <v>152</v>
-      </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
       </c>
       <c r="E42" t="s">
-        <v>153</v>
-      </c>
-      <c r="F42" t="s">
-        <v>78</v>
+        <v>152</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G42" t="s">
         <v>30</v>
@@ -4217,22 +4489,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>153</v>
+      </c>
+      <c r="B43" t="s">
         <v>154</v>
       </c>
-      <c r="B43" t="s">
-        <v>155</v>
-      </c>
       <c r="C43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
       </c>
       <c r="E43" t="s">
-        <v>156</v>
-      </c>
-      <c r="F43" t="s">
-        <v>29</v>
+        <v>155</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G43" t="s">
         <v>13</v>
@@ -4240,10 +4512,10 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>156</v>
+      </c>
+      <c r="B44" t="s">
         <v>157</v>
-      </c>
-      <c r="B44" t="s">
-        <v>158</v>
       </c>
       <c r="C44" t="s">
         <v>21</v>
@@ -4252,10 +4524,10 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>159</v>
-      </c>
-      <c r="F44" t="s">
-        <v>29</v>
+        <v>158</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G44" t="s">
         <v>13</v>
@@ -4263,10 +4535,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>159</v>
+      </c>
+      <c r="B45" t="s">
         <v>160</v>
-      </c>
-      <c r="B45" t="s">
-        <v>161</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
@@ -4275,33 +4547,33 @@
         <v>27</v>
       </c>
       <c r="E45" t="s">
-        <v>162</v>
-      </c>
-      <c r="F45" t="s">
-        <v>78</v>
+        <v>161</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>162</v>
+      </c>
+      <c r="B46" t="s">
         <v>163</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
+        <v>59</v>
+      </c>
+      <c r="D46" t="s">
+        <v>32</v>
+      </c>
+      <c r="E46" t="s">
         <v>164</v>
       </c>
-      <c r="C46" t="s">
-        <v>60</v>
-      </c>
-      <c r="D46" t="s">
-        <v>33</v>
-      </c>
-      <c r="E46" t="s">
-        <v>165</v>
-      </c>
-      <c r="F46" t="s">
-        <v>12</v>
+      <c r="F46" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G46" t="s">
         <v>30</v>
@@ -4309,22 +4581,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>165</v>
+      </c>
+      <c r="B47" t="s">
         <v>166</v>
-      </c>
-      <c r="B47" t="s">
-        <v>167</v>
       </c>
       <c r="C47" t="s">
         <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E47" t="s">
-        <v>168</v>
-      </c>
-      <c r="F47" t="s">
-        <v>78</v>
+        <v>167</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G47" t="s">
         <v>24</v>
@@ -4332,22 +4604,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>168</v>
+      </c>
+      <c r="B48" t="s">
         <v>169</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48" t="s">
         <v>170</v>
       </c>
-      <c r="C48" t="s">
-        <v>43</v>
-      </c>
-      <c r="D48" t="s">
-        <v>44</v>
-      </c>
-      <c r="E48" t="s">
-        <v>171</v>
-      </c>
-      <c r="F48" t="s">
-        <v>12</v>
+      <c r="F48" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G48" t="s">
         <v>30</v>
@@ -4355,22 +4627,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>171</v>
+      </c>
+      <c r="B49" t="s">
         <v>172</v>
-      </c>
-      <c r="B49" t="s">
-        <v>173</v>
       </c>
       <c r="C49" t="s">
         <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E49" t="s">
-        <v>174</v>
-      </c>
-      <c r="F49" t="s">
-        <v>35</v>
+        <v>173</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="G49" t="s">
         <v>13</v>
@@ -4378,45 +4650,45 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>174</v>
+      </c>
+      <c r="B50" t="s">
         <v>175</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" t="s">
+        <v>51</v>
+      </c>
+      <c r="E50" t="s">
         <v>176</v>
-      </c>
-      <c r="C50" t="s">
-        <v>60</v>
-      </c>
-      <c r="D50" t="s">
-        <v>52</v>
-      </c>
-      <c r="E50" t="s">
-        <v>177</v>
       </c>
       <c r="F50" t="s">
         <v>29</v>
       </c>
       <c r="G50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>177</v>
+      </c>
+      <c r="B51" t="s">
         <v>178</v>
-      </c>
-      <c r="B51" t="s">
-        <v>179</v>
       </c>
       <c r="C51" t="s">
         <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E51" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G51" t="s">
         <v>13</v>
@@ -4424,45 +4696,45 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>180</v>
+      </c>
+      <c r="B52" t="s">
         <v>181</v>
       </c>
-      <c r="B52" t="s">
-        <v>182</v>
-      </c>
       <c r="C52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F52" t="s">
         <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>183</v>
+      </c>
+      <c r="B53" t="s">
         <v>184</v>
       </c>
-      <c r="B53" t="s">
-        <v>185</v>
-      </c>
       <c r="C53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
       </c>
       <c r="E53" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F53" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G53" t="s">
         <v>24</v>
@@ -4470,45 +4742,45 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>186</v>
+      </c>
+      <c r="B54" t="s">
         <v>187</v>
       </c>
-      <c r="B54" t="s">
-        <v>188</v>
-      </c>
       <c r="C54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D54" t="s">
         <v>22</v>
       </c>
       <c r="E54" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" t="s">
         <v>29</v>
       </c>
       <c r="G54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>189</v>
+      </c>
+      <c r="B55" t="s">
         <v>190</v>
       </c>
-      <c r="B55" t="s">
-        <v>191</v>
-      </c>
       <c r="C55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
         <v>27</v>
       </c>
       <c r="E55" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s">
         <v>30</v>
@@ -4516,45 +4788,45 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>192</v>
+      </c>
+      <c r="B56" t="s">
         <v>193</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
+        <v>42</v>
+      </c>
+      <c r="D56" t="s">
+        <v>32</v>
+      </c>
+      <c r="E56" t="s">
         <v>194</v>
-      </c>
-      <c r="C56" t="s">
-        <v>43</v>
-      </c>
-      <c r="D56" t="s">
-        <v>33</v>
-      </c>
-      <c r="E56" t="s">
-        <v>195</v>
       </c>
       <c r="F56" t="s">
         <v>29</v>
       </c>
       <c r="G56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>195</v>
+      </c>
+      <c r="B57" t="s">
         <v>196</v>
-      </c>
-      <c r="B57" t="s">
-        <v>197</v>
       </c>
       <c r="C57" t="s">
         <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E57" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s">
         <v>13</v>
@@ -4562,22 +4834,22 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" t="s">
         <v>199</v>
-      </c>
-      <c r="B58" t="s">
-        <v>200</v>
       </c>
       <c r="C58" t="s">
         <v>16</v>
       </c>
       <c r="D58" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E58" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G58" t="s">
         <v>24</v>
@@ -4585,19 +4857,19 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>201</v>
+      </c>
+      <c r="B59" t="s">
         <v>202</v>
-      </c>
-      <c r="B59" t="s">
-        <v>203</v>
       </c>
       <c r="C59" t="s">
         <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E59" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F59" t="s">
         <v>29</v>
@@ -4608,19 +4880,19 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>204</v>
+      </c>
+      <c r="B60" t="s">
         <v>205</v>
-      </c>
-      <c r="B60" t="s">
-        <v>206</v>
       </c>
       <c r="C60" t="s">
         <v>21</v>
       </c>
       <c r="D60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E60" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F60" t="s">
         <v>29</v>
@@ -4631,19 +4903,19 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>207</v>
+      </c>
+      <c r="B61" t="s">
         <v>208</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
+        <v>69</v>
+      </c>
+      <c r="D61" t="s">
+        <v>55</v>
+      </c>
+      <c r="E61" t="s">
         <v>209</v>
-      </c>
-      <c r="C61" t="s">
-        <v>70</v>
-      </c>
-      <c r="D61" t="s">
-        <v>56</v>
-      </c>
-      <c r="E61" t="s">
-        <v>210</v>
       </c>
       <c r="F61" t="s">
         <v>12</v>
@@ -4654,45 +4926,45 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>210</v>
+      </c>
+      <c r="B62" t="s">
         <v>211</v>
       </c>
-      <c r="B62" t="s">
-        <v>212</v>
-      </c>
       <c r="C62" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D62" t="s">
         <v>10</v>
       </c>
       <c r="E62" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F62" t="s">
         <v>29</v>
       </c>
       <c r="G62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>213</v>
+      </c>
+      <c r="B63" t="s">
         <v>214</v>
       </c>
-      <c r="B63" t="s">
-        <v>215</v>
-      </c>
       <c r="C63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D63" t="s">
         <v>17</v>
       </c>
       <c r="E63" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G63" t="s">
         <v>13</v>
@@ -4700,10 +4972,10 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>216</v>
+      </c>
+      <c r="B64" t="s">
         <v>217</v>
-      </c>
-      <c r="B64" t="s">
-        <v>218</v>
       </c>
       <c r="C64" t="s">
         <v>9</v>
@@ -4712,10 +4984,10 @@
         <v>22</v>
       </c>
       <c r="E64" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F64" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G64" t="s">
         <v>13</v>
@@ -4723,10 +4995,10 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>219</v>
+      </c>
+      <c r="B65" t="s">
         <v>220</v>
-      </c>
-      <c r="B65" t="s">
-        <v>221</v>
       </c>
       <c r="C65" t="s">
         <v>16</v>
@@ -4735,56 +5007,56 @@
         <v>27</v>
       </c>
       <c r="E65" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>222</v>
+      </c>
+      <c r="B66" t="s">
         <v>223</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
+        <v>69</v>
+      </c>
+      <c r="D66" t="s">
+        <v>32</v>
+      </c>
+      <c r="E66" t="s">
         <v>224</v>
       </c>
-      <c r="C66" t="s">
-        <v>70</v>
-      </c>
-      <c r="D66" t="s">
-        <v>33</v>
-      </c>
-      <c r="E66" t="s">
-        <v>225</v>
-      </c>
       <c r="F66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>225</v>
+      </c>
+      <c r="B67" t="s">
         <v>226</v>
-      </c>
-      <c r="B67" t="s">
-        <v>227</v>
       </c>
       <c r="C67" t="s">
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E67" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G67" t="s">
         <v>30</v>
@@ -4792,19 +5064,19 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>228</v>
+      </c>
+      <c r="B68" t="s">
         <v>229</v>
-      </c>
-      <c r="B68" t="s">
-        <v>230</v>
       </c>
       <c r="C68" t="s">
         <v>16</v>
       </c>
       <c r="D68" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E68" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F68" t="s">
         <v>29</v>
@@ -4815,22 +5087,22 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>231</v>
+      </c>
+      <c r="B69" t="s">
         <v>232</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
+        <v>59</v>
+      </c>
+      <c r="D69" t="s">
+        <v>47</v>
+      </c>
+      <c r="E69" t="s">
         <v>233</v>
       </c>
-      <c r="C69" t="s">
-        <v>60</v>
-      </c>
-      <c r="D69" t="s">
-        <v>48</v>
-      </c>
-      <c r="E69" t="s">
-        <v>234</v>
-      </c>
       <c r="F69" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G69" t="s">
         <v>13</v>
@@ -4838,22 +5110,22 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>234</v>
+      </c>
+      <c r="B70" t="s">
         <v>235</v>
-      </c>
-      <c r="B70" t="s">
-        <v>236</v>
       </c>
       <c r="C70" t="s">
         <v>16</v>
       </c>
       <c r="D70" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E70" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G70" t="s">
         <v>24</v>
@@ -4861,33 +5133,33 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>237</v>
+      </c>
+      <c r="B71" t="s">
         <v>238</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
+        <v>59</v>
+      </c>
+      <c r="D71" t="s">
+        <v>55</v>
+      </c>
+      <c r="E71" t="s">
         <v>239</v>
-      </c>
-      <c r="C71" t="s">
-        <v>60</v>
-      </c>
-      <c r="D71" t="s">
-        <v>56</v>
-      </c>
-      <c r="E71" t="s">
-        <v>240</v>
       </c>
       <c r="F71" t="s">
         <v>12</v>
       </c>
       <c r="G71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>240</v>
+      </c>
+      <c r="B72" t="s">
         <v>241</v>
-      </c>
-      <c r="B72" t="s">
-        <v>242</v>
       </c>
       <c r="C72" t="s">
         <v>21</v>
@@ -4896,10 +5168,10 @@
         <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F72" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G72" t="s">
         <v>30</v>
@@ -4907,10 +5179,10 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>243</v>
+      </c>
+      <c r="B73" t="s">
         <v>244</v>
-      </c>
-      <c r="B73" t="s">
-        <v>245</v>
       </c>
       <c r="C73" t="s">
         <v>16</v>
@@ -4919,7 +5191,7 @@
         <v>17</v>
       </c>
       <c r="E73" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F73" t="s">
         <v>29</v>
@@ -4930,10 +5202,10 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>246</v>
+      </c>
+      <c r="B74" t="s">
         <v>247</v>
-      </c>
-      <c r="B74" t="s">
-        <v>248</v>
       </c>
       <c r="C74" t="s">
         <v>16</v>
@@ -4942,7 +5214,7 @@
         <v>22</v>
       </c>
       <c r="E74" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F74" t="s">
         <v>29</v>
@@ -4953,19 +5225,19 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>249</v>
+      </c>
+      <c r="B75" t="s">
         <v>250</v>
       </c>
-      <c r="B75" t="s">
-        <v>251</v>
-      </c>
       <c r="C75" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D75" t="s">
         <v>27</v>
       </c>
       <c r="E75" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F75" t="s">
         <v>29</v>
@@ -4976,45 +5248,45 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>252</v>
+      </c>
+      <c r="B76" t="s">
         <v>253</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
+        <v>69</v>
+      </c>
+      <c r="D76" t="s">
+        <v>32</v>
+      </c>
+      <c r="E76" t="s">
         <v>254</v>
       </c>
-      <c r="C76" t="s">
-        <v>70</v>
-      </c>
-      <c r="D76" t="s">
-        <v>33</v>
-      </c>
-      <c r="E76" t="s">
-        <v>255</v>
-      </c>
       <c r="F76" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>255</v>
+      </c>
+      <c r="B77" t="s">
         <v>256</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
+        <v>59</v>
+      </c>
+      <c r="D77" t="s">
+        <v>37</v>
+      </c>
+      <c r="E77" t="s">
         <v>257</v>
       </c>
-      <c r="C77" t="s">
-        <v>60</v>
-      </c>
-      <c r="D77" t="s">
-        <v>38</v>
-      </c>
-      <c r="E77" t="s">
-        <v>258</v>
-      </c>
       <c r="F77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G77" t="s">
         <v>30</v>
@@ -5022,19 +5294,19 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>258</v>
+      </c>
+      <c r="B78" t="s">
         <v>259</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
+        <v>59</v>
+      </c>
+      <c r="D78" t="s">
+        <v>43</v>
+      </c>
+      <c r="E78" t="s">
         <v>260</v>
-      </c>
-      <c r="C78" t="s">
-        <v>60</v>
-      </c>
-      <c r="D78" t="s">
-        <v>44</v>
-      </c>
-      <c r="E78" t="s">
-        <v>261</v>
       </c>
       <c r="F78" t="s">
         <v>12</v>
@@ -5045,45 +5317,45 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>261</v>
+      </c>
+      <c r="B79" t="s">
         <v>262</v>
-      </c>
-      <c r="B79" t="s">
-        <v>263</v>
       </c>
       <c r="C79" t="s">
         <v>16</v>
       </c>
       <c r="D79" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E79" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F79" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G79" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>264</v>
+      </c>
+      <c r="B80" t="s">
         <v>265</v>
-      </c>
-      <c r="B80" t="s">
-        <v>266</v>
       </c>
       <c r="C80" t="s">
         <v>9</v>
       </c>
       <c r="D80" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E80" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F80" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G80" t="s">
         <v>24</v>
@@ -5091,33 +5363,33 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>267</v>
+      </c>
+      <c r="B81" t="s">
         <v>268</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
+        <v>42</v>
+      </c>
+      <c r="D81" t="s">
+        <v>55</v>
+      </c>
+      <c r="E81" t="s">
         <v>269</v>
-      </c>
-      <c r="C81" t="s">
-        <v>43</v>
-      </c>
-      <c r="D81" t="s">
-        <v>56</v>
-      </c>
-      <c r="E81" t="s">
-        <v>270</v>
       </c>
       <c r="F81" t="s">
         <v>29</v>
       </c>
       <c r="G81" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>270</v>
+      </c>
+      <c r="B82" t="s">
         <v>271</v>
-      </c>
-      <c r="B82" t="s">
-        <v>272</v>
       </c>
       <c r="C82" t="s">
         <v>21</v>
@@ -5126,7 +5398,7 @@
         <v>10</v>
       </c>
       <c r="E82" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F82" t="s">
         <v>12</v>
@@ -5137,22 +5409,22 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>273</v>
+      </c>
+      <c r="B83" t="s">
         <v>274</v>
       </c>
-      <c r="B83" t="s">
-        <v>275</v>
-      </c>
       <c r="C83" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D83" t="s">
         <v>17</v>
       </c>
       <c r="E83" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F83" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G83" t="s">
         <v>30</v>
@@ -5160,19 +5432,19 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>276</v>
+      </c>
+      <c r="B84" t="s">
         <v>277</v>
       </c>
-      <c r="B84" t="s">
-        <v>278</v>
-      </c>
       <c r="C84" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D84" t="s">
         <v>22</v>
       </c>
       <c r="E84" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F84" t="s">
         <v>12</v>
@@ -5183,42 +5455,42 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>279</v>
+      </c>
+      <c r="B85" t="s">
         <v>280</v>
       </c>
-      <c r="B85" t="s">
-        <v>281</v>
-      </c>
       <c r="C85" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D85" t="s">
         <v>27</v>
       </c>
       <c r="E85" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F85" t="s">
         <v>29</v>
       </c>
       <c r="G85" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>282</v>
+      </c>
+      <c r="B86" t="s">
         <v>283</v>
-      </c>
-      <c r="B86" t="s">
-        <v>284</v>
       </c>
       <c r="C86" t="s">
         <v>21</v>
       </c>
       <c r="D86" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E86" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F86" t="s">
         <v>12</v>
@@ -5229,22 +5501,22 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>285</v>
+      </c>
+      <c r="B87" t="s">
         <v>286</v>
-      </c>
-      <c r="B87" t="s">
-        <v>287</v>
       </c>
       <c r="C87" t="s">
         <v>9</v>
       </c>
       <c r="D87" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E87" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F87" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G87" t="s">
         <v>24</v>
@@ -5252,19 +5524,19 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>288</v>
+      </c>
+      <c r="B88" t="s">
         <v>289</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
+        <v>59</v>
+      </c>
+      <c r="D88" t="s">
+        <v>43</v>
+      </c>
+      <c r="E88" t="s">
         <v>290</v>
-      </c>
-      <c r="C88" t="s">
-        <v>60</v>
-      </c>
-      <c r="D88" t="s">
-        <v>44</v>
-      </c>
-      <c r="E88" t="s">
-        <v>291</v>
       </c>
       <c r="F88" t="s">
         <v>12</v>
@@ -5275,22 +5547,22 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>291</v>
+      </c>
+      <c r="B89" t="s">
         <v>292</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
+        <v>69</v>
+      </c>
+      <c r="D89" t="s">
+        <v>47</v>
+      </c>
+      <c r="E89" t="s">
         <v>293</v>
       </c>
-      <c r="C89" t="s">
-        <v>70</v>
-      </c>
-      <c r="D89" t="s">
-        <v>48</v>
-      </c>
-      <c r="E89" t="s">
-        <v>294</v>
-      </c>
       <c r="F89" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G89" t="s">
         <v>13</v>
@@ -5298,45 +5570,45 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>294</v>
+      </c>
+      <c r="B90" t="s">
         <v>295</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
+        <v>42</v>
+      </c>
+      <c r="D90" t="s">
+        <v>51</v>
+      </c>
+      <c r="E90" t="s">
         <v>296</v>
       </c>
-      <c r="C90" t="s">
-        <v>43</v>
-      </c>
-      <c r="D90" t="s">
-        <v>52</v>
-      </c>
-      <c r="E90" t="s">
-        <v>297</v>
-      </c>
       <c r="F90" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G90" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>297</v>
+      </c>
+      <c r="B91" t="s">
         <v>298</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
+        <v>42</v>
+      </c>
+      <c r="D91" t="s">
+        <v>55</v>
+      </c>
+      <c r="E91" t="s">
         <v>299</v>
       </c>
-      <c r="C91" t="s">
-        <v>43</v>
-      </c>
-      <c r="D91" t="s">
-        <v>56</v>
-      </c>
-      <c r="E91" t="s">
-        <v>300</v>
-      </c>
       <c r="F91" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G91" t="s">
         <v>13</v>
@@ -5344,10 +5616,10 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>300</v>
+      </c>
+      <c r="B92" t="s">
         <v>301</v>
-      </c>
-      <c r="B92" t="s">
-        <v>302</v>
       </c>
       <c r="C92" t="s">
         <v>21</v>
@@ -5356,21 +5628,21 @@
         <v>10</v>
       </c>
       <c r="E92" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F92" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>303</v>
+      </c>
+      <c r="B93" t="s">
         <v>304</v>
-      </c>
-      <c r="B93" t="s">
-        <v>305</v>
       </c>
       <c r="C93" t="s">
         <v>21</v>
@@ -5379,10 +5651,10 @@
         <v>17</v>
       </c>
       <c r="E93" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F93" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G93" t="s">
         <v>24</v>
@@ -5390,10 +5662,10 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>306</v>
+      </c>
+      <c r="B94" t="s">
         <v>307</v>
-      </c>
-      <c r="B94" t="s">
-        <v>308</v>
       </c>
       <c r="C94" t="s">
         <v>9</v>
@@ -5402,7 +5674,7 @@
         <v>22</v>
       </c>
       <c r="E94" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F94" t="s">
         <v>12</v>
@@ -5413,22 +5685,22 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>309</v>
+      </c>
+      <c r="B95" t="s">
         <v>310</v>
       </c>
-      <c r="B95" t="s">
-        <v>311</v>
-      </c>
       <c r="C95" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D95" t="s">
         <v>27</v>
       </c>
       <c r="E95" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F95" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G95" t="s">
         <v>13</v>
@@ -5436,19 +5708,19 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
+        <v>312</v>
+      </c>
+      <c r="B96" t="s">
         <v>313</v>
-      </c>
-      <c r="B96" t="s">
-        <v>314</v>
       </c>
       <c r="C96" t="s">
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E96" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F96" t="s">
         <v>12</v>
@@ -5459,19 +5731,19 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>315</v>
+      </c>
+      <c r="B97" t="s">
         <v>316</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
+        <v>69</v>
+      </c>
+      <c r="D97" t="s">
+        <v>37</v>
+      </c>
+      <c r="E97" t="s">
         <v>317</v>
-      </c>
-      <c r="C97" t="s">
-        <v>70</v>
-      </c>
-      <c r="D97" t="s">
-        <v>38</v>
-      </c>
-      <c r="E97" t="s">
-        <v>318</v>
       </c>
       <c r="F97" t="s">
         <v>29</v>
@@ -5482,22 +5754,22 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>318</v>
+      </c>
+      <c r="B98" t="s">
         <v>319</v>
-      </c>
-      <c r="B98" t="s">
-        <v>320</v>
       </c>
       <c r="C98" t="s">
         <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E98" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F98" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G98" t="s">
         <v>13</v>
@@ -5505,45 +5777,45 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>321</v>
+      </c>
+      <c r="B99" t="s">
         <v>322</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
+        <v>59</v>
+      </c>
+      <c r="D99" t="s">
+        <v>47</v>
+      </c>
+      <c r="E99" t="s">
         <v>323</v>
-      </c>
-      <c r="C99" t="s">
-        <v>60</v>
-      </c>
-      <c r="D99" t="s">
-        <v>48</v>
-      </c>
-      <c r="E99" t="s">
-        <v>324</v>
       </c>
       <c r="F99" t="s">
         <v>12</v>
       </c>
       <c r="G99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>324</v>
+      </c>
+      <c r="B100" t="s">
         <v>325</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
+        <v>42</v>
+      </c>
+      <c r="D100" t="s">
+        <v>51</v>
+      </c>
+      <c r="E100" t="s">
         <v>326</v>
       </c>
-      <c r="C100" t="s">
-        <v>43</v>
-      </c>
-      <c r="D100" t="s">
-        <v>52</v>
-      </c>
-      <c r="E100" t="s">
-        <v>327</v>
-      </c>
       <c r="F100" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G100" t="s">
         <v>24</v>
@@ -5551,19 +5823,19 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>327</v>
+      </c>
+      <c r="B101" t="s">
         <v>328</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
+        <v>59</v>
+      </c>
+      <c r="D101" t="s">
+        <v>55</v>
+      </c>
+      <c r="E101" t="s">
         <v>329</v>
-      </c>
-      <c r="C101" t="s">
-        <v>60</v>
-      </c>
-      <c r="D101" t="s">
-        <v>56</v>
-      </c>
-      <c r="E101" t="s">
-        <v>330</v>
       </c>
       <c r="F101" t="s">
         <v>29</v>
@@ -5573,11 +5845,16 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{450CCFCC-94DC-45A2-A9F2-5C47E8BAC1C4}"/>
+    <hyperlink ref="F3:F49" r:id="rId2" display="https://cdn-icons-png.flaticon.com/512/1/1443.png" xr:uid="{32FD3DE8-479D-4A38-B20C-D7B771CC5CFB}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{9B702E69-F15B-461E-9186-5A027EABA066}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5607,19 +5884,19 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B2" t="s">
         <v>331</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" t="s">
         <v>332</v>
       </c>
-      <c r="C2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>333</v>
-      </c>
-      <c r="E2" t="s">
-        <v>334</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -5630,22 +5907,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B3" t="s">
         <v>335</v>
-      </c>
-      <c r="B3" t="s">
-        <v>336</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
       </c>
       <c r="D3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E3" t="s">
         <v>337</v>
       </c>
-      <c r="E3" t="s">
-        <v>338</v>
-      </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s">
         <v>30</v>
@@ -5653,22 +5930,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B4" t="s">
         <v>339</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
         <v>340</v>
       </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>341</v>
       </c>
-      <c r="E4" t="s">
-        <v>342</v>
-      </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
         <v>30</v>
@@ -5676,22 +5953,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B5" t="s">
         <v>343</v>
-      </c>
-      <c r="B5" t="s">
-        <v>344</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
       <c r="D5" t="s">
+        <v>344</v>
+      </c>
+      <c r="E5" t="s">
         <v>345</v>
       </c>
-      <c r="E5" t="s">
-        <v>346</v>
-      </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
@@ -5699,22 +5976,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B6" t="s">
         <v>347</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
         <v>348</v>
       </c>
-      <c r="C6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>349</v>
       </c>
-      <c r="E6" t="s">
-        <v>350</v>
-      </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -5722,19 +5999,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B7" t="s">
         <v>351</v>
-      </c>
-      <c r="B7" t="s">
-        <v>352</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>352</v>
+      </c>
+      <c r="E7" t="s">
         <v>353</v>
-      </c>
-      <c r="E7" t="s">
-        <v>354</v>
       </c>
       <c r="F7" t="s">
         <v>29</v>
@@ -5745,22 +6022,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>354</v>
+      </c>
+      <c r="B8" t="s">
         <v>355</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" t="s">
         <v>356</v>
       </c>
-      <c r="C8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>357</v>
       </c>
-      <c r="E8" t="s">
-        <v>358</v>
-      </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -5768,42 +6045,42 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B9" t="s">
         <v>359</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" t="s">
         <v>360</v>
       </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>361</v>
       </c>
-      <c r="E9" t="s">
-        <v>362</v>
-      </c>
       <c r="F9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>362</v>
+      </c>
+      <c r="B10" t="s">
         <v>363</v>
-      </c>
-      <c r="B10" t="s">
-        <v>364</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
       </c>
       <c r="D10" t="s">
+        <v>364</v>
+      </c>
+      <c r="E10" t="s">
         <v>365</v>
-      </c>
-      <c r="E10" t="s">
-        <v>366</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -5814,42 +6091,42 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>366</v>
+      </c>
+      <c r="B11" t="s">
         <v>367</v>
-      </c>
-      <c r="B11" t="s">
-        <v>368</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>368</v>
+      </c>
+      <c r="E11" t="s">
         <v>369</v>
       </c>
-      <c r="E11" t="s">
-        <v>370</v>
-      </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B12" t="s">
         <v>371</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>332</v>
+      </c>
+      <c r="E12" t="s">
         <v>372</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>333</v>
-      </c>
-      <c r="E12" t="s">
-        <v>373</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -5860,22 +6137,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>373</v>
+      </c>
+      <c r="B13" t="s">
         <v>374</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>336</v>
+      </c>
+      <c r="E13" t="s">
         <v>375</v>
       </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>337</v>
-      </c>
-      <c r="E13" t="s">
-        <v>376</v>
-      </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -5883,22 +6160,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>376</v>
+      </c>
+      <c r="B14" t="s">
         <v>377</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" t="s">
+        <v>340</v>
+      </c>
+      <c r="E14" t="s">
         <v>378</v>
       </c>
-      <c r="C14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" t="s">
-        <v>341</v>
-      </c>
-      <c r="E14" t="s">
-        <v>379</v>
-      </c>
       <c r="F14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s">
         <v>30</v>
@@ -5906,42 +6183,42 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>379</v>
+      </c>
+      <c r="B15" t="s">
         <v>380</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
+        <v>344</v>
+      </c>
+      <c r="E15" t="s">
         <v>381</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" t="s">
-        <v>345</v>
-      </c>
-      <c r="E15" t="s">
-        <v>382</v>
       </c>
       <c r="F15" t="s">
         <v>29</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>382</v>
+      </c>
+      <c r="B16" t="s">
         <v>383</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>348</v>
+      </c>
+      <c r="E16" t="s">
         <v>384</v>
-      </c>
-      <c r="C16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" t="s">
-        <v>349</v>
-      </c>
-      <c r="E16" t="s">
-        <v>385</v>
       </c>
       <c r="F16" t="s">
         <v>29</v>
@@ -5952,42 +6229,42 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>385</v>
+      </c>
+      <c r="B17" t="s">
         <v>386</v>
-      </c>
-      <c r="B17" t="s">
-        <v>387</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F17" t="s">
         <v>29</v>
       </c>
       <c r="G17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>388</v>
+      </c>
+      <c r="B18" t="s">
         <v>389</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
+        <v>356</v>
+      </c>
+      <c r="E18" t="s">
         <v>390</v>
-      </c>
-      <c r="C18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" t="s">
-        <v>357</v>
-      </c>
-      <c r="E18" t="s">
-        <v>391</v>
       </c>
       <c r="F18" t="s">
         <v>29</v>
@@ -5998,19 +6275,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>391</v>
+      </c>
+      <c r="B19" t="s">
         <v>392</v>
-      </c>
-      <c r="B19" t="s">
-        <v>393</v>
       </c>
       <c r="C19" t="s">
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E19" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -6021,19 +6298,19 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>394</v>
+      </c>
+      <c r="B20" t="s">
         <v>395</v>
-      </c>
-      <c r="B20" t="s">
-        <v>396</v>
       </c>
       <c r="C20" t="s">
         <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E20" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -6044,45 +6321,45 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>397</v>
+      </c>
+      <c r="B21" t="s">
         <v>398</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" t="s">
+        <v>368</v>
+      </c>
+      <c r="E21" t="s">
         <v>399</v>
-      </c>
-      <c r="C21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" t="s">
-        <v>369</v>
-      </c>
-      <c r="E21" t="s">
-        <v>400</v>
       </c>
       <c r="F21" t="s">
         <v>29</v>
       </c>
       <c r="G21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>400</v>
+      </c>
+      <c r="B22" t="s">
         <v>401</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
+        <v>332</v>
+      </c>
+      <c r="E22" t="s">
         <v>402</v>
       </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" t="s">
-        <v>333</v>
-      </c>
-      <c r="E22" t="s">
-        <v>403</v>
-      </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
@@ -6090,45 +6367,45 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>403</v>
+      </c>
+      <c r="B23" t="s">
         <v>404</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" t="s">
+        <v>336</v>
+      </c>
+      <c r="E23" t="s">
         <v>405</v>
       </c>
-      <c r="C23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" t="s">
-        <v>337</v>
-      </c>
-      <c r="E23" t="s">
-        <v>406</v>
-      </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>406</v>
+      </c>
+      <c r="B24" t="s">
         <v>407</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
+        <v>340</v>
+      </c>
+      <c r="E24" t="s">
         <v>408</v>
       </c>
-      <c r="C24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" t="s">
-        <v>341</v>
-      </c>
-      <c r="E24" t="s">
-        <v>409</v>
-      </c>
       <c r="F24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s">
         <v>24</v>
@@ -6136,42 +6413,42 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>409</v>
+      </c>
+      <c r="B25" t="s">
         <v>410</v>
-      </c>
-      <c r="B25" t="s">
-        <v>411</v>
       </c>
       <c r="C25" t="s">
         <v>21</v>
       </c>
       <c r="D25" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E25" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>412</v>
+      </c>
+      <c r="B26" t="s">
         <v>413</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" t="s">
+        <v>348</v>
+      </c>
+      <c r="E26" t="s">
         <v>414</v>
-      </c>
-      <c r="C26" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" t="s">
-        <v>349</v>
-      </c>
-      <c r="E26" t="s">
-        <v>415</v>
       </c>
       <c r="F26" t="s">
         <v>12</v>
@@ -6182,42 +6459,42 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>415</v>
+      </c>
+      <c r="B27" t="s">
         <v>416</v>
-      </c>
-      <c r="B27" t="s">
-        <v>417</v>
       </c>
       <c r="C27" t="s">
         <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E27" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>418</v>
+      </c>
+      <c r="B28" t="s">
         <v>419</v>
-      </c>
-      <c r="B28" t="s">
-        <v>420</v>
       </c>
       <c r="C28" t="s">
         <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
@@ -6228,42 +6505,42 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>421</v>
+      </c>
+      <c r="B29" t="s">
         <v>422</v>
-      </c>
-      <c r="B29" t="s">
-        <v>423</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E29" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>424</v>
+      </c>
+      <c r="B30" t="s">
         <v>425</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" t="s">
+        <v>364</v>
+      </c>
+      <c r="E30" t="s">
         <v>426</v>
-      </c>
-      <c r="C30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" t="s">
-        <v>365</v>
-      </c>
-      <c r="E30" t="s">
-        <v>427</v>
       </c>
       <c r="F30" t="s">
         <v>12</v>
@@ -6274,22 +6551,22 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>427</v>
+      </c>
+      <c r="B31" t="s">
         <v>428</v>
-      </c>
-      <c r="B31" t="s">
-        <v>429</v>
       </c>
       <c r="C31" t="s">
         <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E31" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G31" t="s">
         <v>24</v>
@@ -6297,19 +6574,19 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>430</v>
+      </c>
+      <c r="B32" t="s">
         <v>431</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" t="s">
+        <v>332</v>
+      </c>
+      <c r="E32" t="s">
         <v>432</v>
-      </c>
-      <c r="C32" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" t="s">
-        <v>333</v>
-      </c>
-      <c r="E32" t="s">
-        <v>433</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
@@ -6320,45 +6597,45 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>433</v>
+      </c>
+      <c r="B33" t="s">
         <v>434</v>
-      </c>
-      <c r="B33" t="s">
-        <v>435</v>
       </c>
       <c r="C33" t="s">
         <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E33" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>436</v>
+      </c>
+      <c r="B34" t="s">
         <v>437</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" t="s">
+        <v>340</v>
+      </c>
+      <c r="E34" t="s">
         <v>438</v>
       </c>
-      <c r="C34" t="s">
-        <v>60</v>
-      </c>
-      <c r="D34" t="s">
-        <v>341</v>
-      </c>
-      <c r="E34" t="s">
-        <v>439</v>
-      </c>
       <c r="F34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
@@ -6366,22 +6643,22 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>439</v>
+      </c>
+      <c r="B35" t="s">
         <v>440</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" t="s">
+        <v>344</v>
+      </c>
+      <c r="E35" t="s">
         <v>441</v>
       </c>
-      <c r="C35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" t="s">
-        <v>345</v>
-      </c>
-      <c r="E35" t="s">
-        <v>442</v>
-      </c>
       <c r="F35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s">
         <v>24</v>
@@ -6389,19 +6666,19 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>442</v>
+      </c>
+      <c r="B36" t="s">
         <v>443</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" t="s">
+        <v>348</v>
+      </c>
+      <c r="E36" t="s">
         <v>444</v>
-      </c>
-      <c r="C36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" t="s">
-        <v>349</v>
-      </c>
-      <c r="E36" t="s">
-        <v>445</v>
       </c>
       <c r="F36" t="s">
         <v>12</v>
@@ -6412,22 +6689,22 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>445</v>
+      </c>
+      <c r="B37" t="s">
         <v>446</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" t="s">
+        <v>352</v>
+      </c>
+      <c r="E37" t="s">
         <v>447</v>
       </c>
-      <c r="C37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D37" t="s">
-        <v>353</v>
-      </c>
-      <c r="E37" t="s">
-        <v>448</v>
-      </c>
       <c r="F37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s">
         <v>24</v>
@@ -6435,19 +6712,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>448</v>
+      </c>
+      <c r="B38" t="s">
         <v>449</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" t="s">
+        <v>356</v>
+      </c>
+      <c r="E38" t="s">
         <v>450</v>
-      </c>
-      <c r="C38" t="s">
-        <v>43</v>
-      </c>
-      <c r="D38" t="s">
-        <v>357</v>
-      </c>
-      <c r="E38" t="s">
-        <v>451</v>
       </c>
       <c r="F38" t="s">
         <v>12</v>
@@ -6458,42 +6735,42 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>451</v>
+      </c>
+      <c r="B39" t="s">
         <v>452</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" t="s">
+        <v>360</v>
+      </c>
+      <c r="E39" t="s">
         <v>453</v>
-      </c>
-      <c r="C39" t="s">
-        <v>60</v>
-      </c>
-      <c r="D39" t="s">
-        <v>361</v>
-      </c>
-      <c r="E39" t="s">
-        <v>454</v>
       </c>
       <c r="F39" t="s">
         <v>12</v>
       </c>
       <c r="G39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>454</v>
+      </c>
+      <c r="B40" t="s">
         <v>455</v>
-      </c>
-      <c r="B40" t="s">
-        <v>456</v>
       </c>
       <c r="C40" t="s">
         <v>9</v>
       </c>
       <c r="D40" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E40" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F40" t="s">
         <v>12</v>
@@ -6504,19 +6781,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>457</v>
+      </c>
+      <c r="B41" t="s">
         <v>458</v>
-      </c>
-      <c r="B41" t="s">
-        <v>459</v>
       </c>
       <c r="C41" t="s">
         <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E41" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F41" t="s">
         <v>12</v>
@@ -6527,22 +6804,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>460</v>
+      </c>
+      <c r="B42" t="s">
         <v>461</v>
-      </c>
-      <c r="B42" t="s">
-        <v>462</v>
       </c>
       <c r="C42" t="s">
         <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E42" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G42" t="s">
         <v>24</v>
@@ -6550,22 +6827,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>463</v>
+      </c>
+      <c r="B43" t="s">
         <v>464</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D43" t="s">
+        <v>336</v>
+      </c>
+      <c r="E43" t="s">
         <v>465</v>
       </c>
-      <c r="C43" t="s">
-        <v>70</v>
-      </c>
-      <c r="D43" t="s">
-        <v>337</v>
-      </c>
-      <c r="E43" t="s">
-        <v>466</v>
-      </c>
       <c r="F43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s">
         <v>30</v>
@@ -6573,45 +6850,45 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>466</v>
+      </c>
+      <c r="B44" t="s">
         <v>467</v>
-      </c>
-      <c r="B44" t="s">
-        <v>468</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
       </c>
       <c r="D44" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E44" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F44" t="s">
         <v>29</v>
       </c>
       <c r="G44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>469</v>
+      </c>
+      <c r="B45" t="s">
         <v>470</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45" t="s">
+        <v>344</v>
+      </c>
+      <c r="E45" t="s">
         <v>471</v>
       </c>
-      <c r="C45" t="s">
-        <v>60</v>
-      </c>
-      <c r="D45" t="s">
-        <v>345</v>
-      </c>
-      <c r="E45" t="s">
-        <v>472</v>
-      </c>
       <c r="F45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G45" t="s">
         <v>30</v>
@@ -6619,19 +6896,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>472</v>
+      </c>
+      <c r="B46" t="s">
         <v>473</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D46" t="s">
+        <v>348</v>
+      </c>
+      <c r="E46" t="s">
         <v>474</v>
-      </c>
-      <c r="C46" t="s">
-        <v>43</v>
-      </c>
-      <c r="D46" t="s">
-        <v>349</v>
-      </c>
-      <c r="E46" t="s">
-        <v>475</v>
       </c>
       <c r="F46" t="s">
         <v>29</v>
@@ -6642,22 +6919,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>475</v>
+      </c>
+      <c r="B47" t="s">
         <v>476</v>
-      </c>
-      <c r="B47" t="s">
-        <v>477</v>
       </c>
       <c r="C47" t="s">
         <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E47" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G47" t="s">
         <v>30</v>
@@ -6665,45 +6942,45 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>478</v>
+      </c>
+      <c r="B48" t="s">
         <v>479</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" t="s">
+        <v>356</v>
+      </c>
+      <c r="E48" t="s">
         <v>480</v>
-      </c>
-      <c r="C48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D48" t="s">
-        <v>357</v>
-      </c>
-      <c r="E48" t="s">
-        <v>481</v>
       </c>
       <c r="F48" t="s">
         <v>29</v>
       </c>
       <c r="G48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>481</v>
+      </c>
+      <c r="B49" t="s">
         <v>482</v>
-      </c>
-      <c r="B49" t="s">
-        <v>483</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E49" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G49" t="s">
         <v>24</v>
@@ -6711,22 +6988,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>484</v>
+      </c>
+      <c r="B50" t="s">
         <v>485</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
+        <v>42</v>
+      </c>
+      <c r="D50" t="s">
+        <v>364</v>
+      </c>
+      <c r="E50" t="s">
         <v>486</v>
       </c>
-      <c r="C50" t="s">
-        <v>43</v>
-      </c>
-      <c r="D50" t="s">
-        <v>365</v>
-      </c>
-      <c r="E50" t="s">
-        <v>487</v>
-      </c>
       <c r="F50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G50" t="s">
         <v>24</v>
@@ -6734,137 +7011,137 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>487</v>
+      </c>
+      <c r="B51" t="s">
         <v>488</v>
-      </c>
-      <c r="B51" t="s">
-        <v>489</v>
       </c>
       <c r="C51" t="s">
         <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E51" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F51" t="s">
         <v>12</v>
       </c>
       <c r="G51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>490</v>
+      </c>
+      <c r="B52" t="s">
         <v>491</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
+        <v>59</v>
+      </c>
+      <c r="D52" t="s">
+        <v>332</v>
+      </c>
+      <c r="E52" t="s">
         <v>492</v>
       </c>
-      <c r="C52" t="s">
-        <v>60</v>
-      </c>
-      <c r="D52" t="s">
-        <v>333</v>
-      </c>
-      <c r="E52" t="s">
-        <v>493</v>
-      </c>
       <c r="F52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>493</v>
+      </c>
+      <c r="B53" t="s">
         <v>494</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
+        <v>69</v>
+      </c>
+      <c r="D53" t="s">
+        <v>336</v>
+      </c>
+      <c r="E53" t="s">
         <v>495</v>
-      </c>
-      <c r="C53" t="s">
-        <v>70</v>
-      </c>
-      <c r="D53" t="s">
-        <v>337</v>
-      </c>
-      <c r="E53" t="s">
-        <v>496</v>
       </c>
       <c r="F53" t="s">
         <v>29</v>
       </c>
       <c r="G53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>496</v>
+      </c>
+      <c r="B54" t="s">
         <v>497</v>
-      </c>
-      <c r="B54" t="s">
-        <v>498</v>
       </c>
       <c r="C54" t="s">
         <v>16</v>
       </c>
       <c r="D54" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E54" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F54" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>499</v>
+      </c>
+      <c r="B55" t="s">
         <v>500</v>
-      </c>
-      <c r="B55" t="s">
-        <v>501</v>
       </c>
       <c r="C55" t="s">
         <v>9</v>
       </c>
       <c r="D55" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E55" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>502</v>
+      </c>
+      <c r="B56" t="s">
         <v>503</v>
-      </c>
-      <c r="B56" t="s">
-        <v>504</v>
       </c>
       <c r="C56" t="s">
         <v>16</v>
       </c>
       <c r="D56" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E56" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G56" t="s">
         <v>24</v>
@@ -6872,45 +7149,45 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>505</v>
+      </c>
+      <c r="B57" t="s">
         <v>506</v>
-      </c>
-      <c r="B57" t="s">
-        <v>507</v>
       </c>
       <c r="C57" t="s">
         <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E57" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>508</v>
+      </c>
+      <c r="B58" t="s">
         <v>509</v>
-      </c>
-      <c r="B58" t="s">
-        <v>510</v>
       </c>
       <c r="C58" t="s">
         <v>16</v>
       </c>
       <c r="D58" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E58" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G58" t="s">
         <v>24</v>
@@ -6918,19 +7195,19 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>511</v>
+      </c>
+      <c r="B59" t="s">
         <v>512</v>
-      </c>
-      <c r="B59" t="s">
-        <v>513</v>
       </c>
       <c r="C59" t="s">
         <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E59" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F59" t="s">
         <v>29</v>
@@ -6941,22 +7218,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>514</v>
+      </c>
+      <c r="B60" t="s">
         <v>515</v>
-      </c>
-      <c r="B60" t="s">
-        <v>516</v>
       </c>
       <c r="C60" t="s">
         <v>16</v>
       </c>
       <c r="D60" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E60" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G60" t="s">
         <v>13</v>
@@ -6964,22 +7241,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>517</v>
+      </c>
+      <c r="B61" t="s">
         <v>518</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
+        <v>69</v>
+      </c>
+      <c r="D61" t="s">
+        <v>368</v>
+      </c>
+      <c r="E61" t="s">
         <v>519</v>
       </c>
-      <c r="C61" t="s">
-        <v>70</v>
-      </c>
-      <c r="D61" t="s">
-        <v>369</v>
-      </c>
-      <c r="E61" t="s">
-        <v>520</v>
-      </c>
       <c r="F61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -6987,19 +7264,19 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>520</v>
+      </c>
+      <c r="B62" t="s">
         <v>521</v>
-      </c>
-      <c r="B62" t="s">
-        <v>522</v>
       </c>
       <c r="C62" t="s">
         <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E62" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F62" t="s">
         <v>29</v>
@@ -7010,19 +7287,19 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>523</v>
+      </c>
+      <c r="B63" t="s">
         <v>524</v>
-      </c>
-      <c r="B63" t="s">
-        <v>525</v>
       </c>
       <c r="C63" t="s">
         <v>16</v>
       </c>
       <c r="D63" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E63" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
@@ -7033,22 +7310,22 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>526</v>
+      </c>
+      <c r="B64" t="s">
         <v>527</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
+        <v>59</v>
+      </c>
+      <c r="D64" t="s">
+        <v>340</v>
+      </c>
+      <c r="E64" t="s">
         <v>528</v>
       </c>
-      <c r="C64" t="s">
-        <v>60</v>
-      </c>
-      <c r="D64" t="s">
-        <v>341</v>
-      </c>
-      <c r="E64" t="s">
-        <v>529</v>
-      </c>
       <c r="F64" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G64" t="s">
         <v>13</v>
@@ -7056,22 +7333,22 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>529</v>
+      </c>
+      <c r="B65" t="s">
         <v>530</v>
-      </c>
-      <c r="B65" t="s">
-        <v>531</v>
       </c>
       <c r="C65" t="s">
         <v>21</v>
       </c>
       <c r="D65" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E65" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G65" t="s">
         <v>24</v>
@@ -7079,22 +7356,22 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>532</v>
+      </c>
+      <c r="B66" t="s">
         <v>533</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
+        <v>59</v>
+      </c>
+      <c r="D66" t="s">
+        <v>348</v>
+      </c>
+      <c r="E66" t="s">
         <v>534</v>
       </c>
-      <c r="C66" t="s">
-        <v>60</v>
-      </c>
-      <c r="D66" t="s">
-        <v>349</v>
-      </c>
-      <c r="E66" t="s">
-        <v>535</v>
-      </c>
       <c r="F66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G66" t="s">
         <v>13</v>
@@ -7102,22 +7379,22 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>535</v>
+      </c>
+      <c r="B67" t="s">
         <v>536</v>
-      </c>
-      <c r="B67" t="s">
-        <v>537</v>
       </c>
       <c r="C67" t="s">
         <v>21</v>
       </c>
       <c r="D67" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E67" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G67" t="s">
         <v>13</v>
@@ -7125,22 +7402,22 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>538</v>
+      </c>
+      <c r="B68" t="s">
         <v>539</v>
-      </c>
-      <c r="B68" t="s">
-        <v>540</v>
       </c>
       <c r="C68" t="s">
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E68" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G68" t="s">
         <v>24</v>
@@ -7148,19 +7425,19 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>541</v>
+      </c>
+      <c r="B69" t="s">
         <v>542</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
+        <v>42</v>
+      </c>
+      <c r="D69" t="s">
+        <v>360</v>
+      </c>
+      <c r="E69" t="s">
         <v>543</v>
-      </c>
-      <c r="C69" t="s">
-        <v>43</v>
-      </c>
-      <c r="D69" t="s">
-        <v>361</v>
-      </c>
-      <c r="E69" t="s">
-        <v>544</v>
       </c>
       <c r="F69" t="s">
         <v>12</v>
@@ -7171,19 +7448,19 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>544</v>
+      </c>
+      <c r="B70" t="s">
         <v>545</v>
-      </c>
-      <c r="B70" t="s">
-        <v>546</v>
       </c>
       <c r="C70" t="s">
         <v>9</v>
       </c>
       <c r="D70" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E70" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F70" t="s">
         <v>29</v>
@@ -7194,19 +7471,19 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>547</v>
+      </c>
+      <c r="B71" t="s">
         <v>548</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
+        <v>69</v>
+      </c>
+      <c r="D71" t="s">
+        <v>368</v>
+      </c>
+      <c r="E71" t="s">
         <v>549</v>
-      </c>
-      <c r="C71" t="s">
-        <v>70</v>
-      </c>
-      <c r="D71" t="s">
-        <v>369</v>
-      </c>
-      <c r="E71" t="s">
-        <v>550</v>
       </c>
       <c r="F71" t="s">
         <v>29</v>
@@ -7217,22 +7494,22 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>550</v>
+      </c>
+      <c r="B72" t="s">
         <v>551</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
+        <v>69</v>
+      </c>
+      <c r="D72" t="s">
+        <v>332</v>
+      </c>
+      <c r="E72" t="s">
         <v>552</v>
       </c>
-      <c r="C72" t="s">
-        <v>70</v>
-      </c>
-      <c r="D72" t="s">
-        <v>333</v>
-      </c>
-      <c r="E72" t="s">
-        <v>553</v>
-      </c>
       <c r="F72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G72" t="s">
         <v>13</v>
@@ -7240,19 +7517,19 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>553</v>
+      </c>
+      <c r="B73" t="s">
         <v>554</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
+        <v>59</v>
+      </c>
+      <c r="D73" t="s">
+        <v>336</v>
+      </c>
+      <c r="E73" t="s">
         <v>555</v>
-      </c>
-      <c r="C73" t="s">
-        <v>60</v>
-      </c>
-      <c r="D73" t="s">
-        <v>337</v>
-      </c>
-      <c r="E73" t="s">
-        <v>556</v>
       </c>
       <c r="F73" t="s">
         <v>29</v>
@@ -7263,22 +7540,22 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>556</v>
+      </c>
+      <c r="B74" t="s">
         <v>557</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
+        <v>42</v>
+      </c>
+      <c r="D74" t="s">
+        <v>340</v>
+      </c>
+      <c r="E74" t="s">
         <v>558</v>
       </c>
-      <c r="C74" t="s">
-        <v>43</v>
-      </c>
-      <c r="D74" t="s">
-        <v>341</v>
-      </c>
-      <c r="E74" t="s">
-        <v>559</v>
-      </c>
       <c r="F74" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G74" t="s">
         <v>13</v>
@@ -7286,22 +7563,22 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>559</v>
+      </c>
+      <c r="B75" t="s">
         <v>560</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
+        <v>42</v>
+      </c>
+      <c r="D75" t="s">
+        <v>344</v>
+      </c>
+      <c r="E75" t="s">
         <v>561</v>
       </c>
-      <c r="C75" t="s">
-        <v>43</v>
-      </c>
-      <c r="D75" t="s">
-        <v>345</v>
-      </c>
-      <c r="E75" t="s">
-        <v>562</v>
-      </c>
       <c r="F75" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G75" t="s">
         <v>30</v>
@@ -7309,19 +7586,19 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>562</v>
+      </c>
+      <c r="B76" t="s">
         <v>563</v>
-      </c>
-      <c r="B76" t="s">
-        <v>564</v>
       </c>
       <c r="C76" t="s">
         <v>16</v>
       </c>
       <c r="D76" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E76" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F76" t="s">
         <v>12</v>
@@ -7332,22 +7609,22 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>565</v>
+      </c>
+      <c r="B77" t="s">
         <v>566</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
+        <v>69</v>
+      </c>
+      <c r="D77" t="s">
+        <v>352</v>
+      </c>
+      <c r="E77" t="s">
         <v>567</v>
       </c>
-      <c r="C77" t="s">
-        <v>70</v>
-      </c>
-      <c r="D77" t="s">
-        <v>353</v>
-      </c>
-      <c r="E77" t="s">
-        <v>568</v>
-      </c>
       <c r="F77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G77" t="s">
         <v>30</v>
@@ -7355,65 +7632,65 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>568</v>
+      </c>
+      <c r="B78" t="s">
         <v>569</v>
-      </c>
-      <c r="B78" t="s">
-        <v>570</v>
       </c>
       <c r="C78" t="s">
         <v>16</v>
       </c>
       <c r="D78" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E78" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F78" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G78" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>571</v>
+      </c>
+      <c r="B79" t="s">
         <v>572</v>
-      </c>
-      <c r="B79" t="s">
-        <v>573</v>
       </c>
       <c r="C79" t="s">
         <v>16</v>
       </c>
       <c r="D79" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E79" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="F79" t="s">
         <v>12</v>
       </c>
       <c r="G79" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>574</v>
+      </c>
+      <c r="B80" t="s">
         <v>575</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
+        <v>42</v>
+      </c>
+      <c r="D80" t="s">
+        <v>364</v>
+      </c>
+      <c r="E80" t="s">
         <v>576</v>
-      </c>
-      <c r="C80" t="s">
-        <v>43</v>
-      </c>
-      <c r="D80" t="s">
-        <v>365</v>
-      </c>
-      <c r="E80" t="s">
-        <v>577</v>
       </c>
       <c r="F80" t="s">
         <v>12</v>
@@ -7424,19 +7701,19 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>577</v>
+      </c>
+      <c r="B81" t="s">
         <v>578</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
+        <v>42</v>
+      </c>
+      <c r="D81" t="s">
+        <v>368</v>
+      </c>
+      <c r="E81" t="s">
         <v>579</v>
-      </c>
-      <c r="C81" t="s">
-        <v>43</v>
-      </c>
-      <c r="D81" t="s">
-        <v>369</v>
-      </c>
-      <c r="E81" t="s">
-        <v>580</v>
       </c>
       <c r="F81" t="s">
         <v>29</v>
@@ -7447,19 +7724,19 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>580</v>
+      </c>
+      <c r="B82" t="s">
         <v>581</v>
-      </c>
-      <c r="B82" t="s">
-        <v>582</v>
       </c>
       <c r="C82" t="s">
         <v>9</v>
       </c>
       <c r="D82" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E82" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F82" t="s">
         <v>29</v>
@@ -7470,19 +7747,19 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>583</v>
+      </c>
+      <c r="B83" t="s">
         <v>584</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
+        <v>69</v>
+      </c>
+      <c r="D83" t="s">
+        <v>336</v>
+      </c>
+      <c r="E83" t="s">
         <v>585</v>
-      </c>
-      <c r="C83" t="s">
-        <v>70</v>
-      </c>
-      <c r="D83" t="s">
-        <v>337</v>
-      </c>
-      <c r="E83" t="s">
-        <v>586</v>
       </c>
       <c r="F83" t="s">
         <v>12</v>
@@ -7493,19 +7770,19 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>586</v>
+      </c>
+      <c r="B84" t="s">
         <v>587</v>
-      </c>
-      <c r="B84" t="s">
-        <v>588</v>
       </c>
       <c r="C84" t="s">
         <v>21</v>
       </c>
       <c r="D84" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E84" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F84" t="s">
         <v>12</v>
@@ -7516,22 +7793,22 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>589</v>
+      </c>
+      <c r="B85" t="s">
         <v>590</v>
-      </c>
-      <c r="B85" t="s">
-        <v>591</v>
       </c>
       <c r="C85" t="s">
         <v>21</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E85" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F85" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G85" t="s">
         <v>13</v>
@@ -7539,22 +7816,22 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>592</v>
+      </c>
+      <c r="B86" t="s">
         <v>593</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
+        <v>42</v>
+      </c>
+      <c r="D86" t="s">
+        <v>348</v>
+      </c>
+      <c r="E86" t="s">
         <v>594</v>
       </c>
-      <c r="C86" t="s">
-        <v>43</v>
-      </c>
-      <c r="D86" t="s">
-        <v>349</v>
-      </c>
-      <c r="E86" t="s">
-        <v>595</v>
-      </c>
       <c r="F86" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G86" t="s">
         <v>24</v>
@@ -7562,19 +7839,19 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>595</v>
+      </c>
+      <c r="B87" t="s">
         <v>596</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
+        <v>59</v>
+      </c>
+      <c r="D87" t="s">
+        <v>352</v>
+      </c>
+      <c r="E87" t="s">
         <v>597</v>
-      </c>
-      <c r="C87" t="s">
-        <v>60</v>
-      </c>
-      <c r="D87" t="s">
-        <v>353</v>
-      </c>
-      <c r="E87" t="s">
-        <v>598</v>
       </c>
       <c r="F87" t="s">
         <v>29</v>
@@ -7585,65 +7862,65 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>598</v>
+      </c>
+      <c r="B88" t="s">
         <v>599</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
+        <v>42</v>
+      </c>
+      <c r="D88" t="s">
+        <v>356</v>
+      </c>
+      <c r="E88" t="s">
         <v>600</v>
       </c>
-      <c r="C88" t="s">
-        <v>43</v>
-      </c>
-      <c r="D88" t="s">
-        <v>357</v>
-      </c>
-      <c r="E88" t="s">
-        <v>601</v>
-      </c>
       <c r="F88" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>601</v>
+      </c>
+      <c r="B89" t="s">
         <v>602</v>
-      </c>
-      <c r="B89" t="s">
-        <v>603</v>
       </c>
       <c r="C89" t="s">
         <v>21</v>
       </c>
       <c r="D89" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E89" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F89" t="s">
         <v>29</v>
       </c>
       <c r="G89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>604</v>
+      </c>
+      <c r="B90" t="s">
         <v>605</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
+        <v>42</v>
+      </c>
+      <c r="D90" t="s">
+        <v>364</v>
+      </c>
+      <c r="E90" t="s">
         <v>606</v>
-      </c>
-      <c r="C90" t="s">
-        <v>43</v>
-      </c>
-      <c r="D90" t="s">
-        <v>365</v>
-      </c>
-      <c r="E90" t="s">
-        <v>607</v>
       </c>
       <c r="F90" t="s">
         <v>29</v>
@@ -7654,19 +7931,19 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>607</v>
+      </c>
+      <c r="B91" t="s">
         <v>608</v>
-      </c>
-      <c r="B91" t="s">
-        <v>609</v>
       </c>
       <c r="C91" t="s">
         <v>9</v>
       </c>
       <c r="D91" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E91" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F91" t="s">
         <v>29</v>
@@ -7677,22 +7954,22 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>610</v>
+      </c>
+      <c r="B92" t="s">
         <v>611</v>
-      </c>
-      <c r="B92" t="s">
-        <v>612</v>
       </c>
       <c r="C92" t="s">
         <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E92" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F92" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G92" t="s">
         <v>13</v>
@@ -7700,22 +7977,22 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>613</v>
+      </c>
+      <c r="B93" t="s">
         <v>614</v>
-      </c>
-      <c r="B93" t="s">
-        <v>615</v>
       </c>
       <c r="C93" t="s">
         <v>9</v>
       </c>
       <c r="D93" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E93" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F93" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G93" t="s">
         <v>30</v>
@@ -7723,19 +8000,19 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>616</v>
+      </c>
+      <c r="B94" t="s">
         <v>617</v>
-      </c>
-      <c r="B94" t="s">
-        <v>618</v>
       </c>
       <c r="C94" t="s">
         <v>9</v>
       </c>
       <c r="D94" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E94" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F94" t="s">
         <v>29</v>
@@ -7746,19 +8023,19 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>619</v>
+      </c>
+      <c r="B95" t="s">
         <v>620</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
+        <v>69</v>
+      </c>
+      <c r="D95" t="s">
+        <v>344</v>
+      </c>
+      <c r="E95" t="s">
         <v>621</v>
-      </c>
-      <c r="C95" t="s">
-        <v>70</v>
-      </c>
-      <c r="D95" t="s">
-        <v>345</v>
-      </c>
-      <c r="E95" t="s">
-        <v>622</v>
       </c>
       <c r="F95" t="s">
         <v>29</v>
@@ -7769,19 +8046,19 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
+        <v>622</v>
+      </c>
+      <c r="B96" t="s">
         <v>623</v>
-      </c>
-      <c r="B96" t="s">
-        <v>624</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E96" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F96" t="s">
         <v>12</v>
@@ -7792,22 +8069,22 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>625</v>
+      </c>
+      <c r="B97" t="s">
         <v>626</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
+        <v>42</v>
+      </c>
+      <c r="D97" t="s">
+        <v>352</v>
+      </c>
+      <c r="E97" t="s">
         <v>627</v>
       </c>
-      <c r="C97" t="s">
-        <v>43</v>
-      </c>
-      <c r="D97" t="s">
-        <v>353</v>
-      </c>
-      <c r="E97" t="s">
-        <v>628</v>
-      </c>
       <c r="F97" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G97" t="s">
         <v>30</v>
@@ -7815,22 +8092,22 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>628</v>
+      </c>
+      <c r="B98" t="s">
         <v>629</v>
-      </c>
-      <c r="B98" t="s">
-        <v>630</v>
       </c>
       <c r="C98" t="s">
         <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E98" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F98" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G98" t="s">
         <v>24</v>
@@ -7838,19 +8115,19 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>631</v>
+      </c>
+      <c r="B99" t="s">
         <v>632</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
+        <v>59</v>
+      </c>
+      <c r="D99" t="s">
+        <v>360</v>
+      </c>
+      <c r="E99" t="s">
         <v>633</v>
-      </c>
-      <c r="C99" t="s">
-        <v>60</v>
-      </c>
-      <c r="D99" t="s">
-        <v>361</v>
-      </c>
-      <c r="E99" t="s">
-        <v>634</v>
       </c>
       <c r="F99" t="s">
         <v>12</v>
@@ -7861,48 +8138,48 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>634</v>
+      </c>
+      <c r="B100" t="s">
         <v>635</v>
-      </c>
-      <c r="B100" t="s">
-        <v>636</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
       </c>
       <c r="D100" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E100" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F100" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G100" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>637</v>
+      </c>
+      <c r="B101" t="s">
         <v>638</v>
-      </c>
-      <c r="B101" t="s">
-        <v>639</v>
       </c>
       <c r="C101" t="s">
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E101" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F101" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -7910,7 +8187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7940,22 +8217,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B2" t="s">
         <v>641</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
         <v>642</v>
       </c>
-      <c r="C2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>643</v>
       </c>
-      <c r="E2" t="s">
-        <v>644</v>
-      </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
@@ -7963,19 +8240,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>644</v>
+      </c>
+      <c r="B3" t="s">
         <v>645</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" t="s">
         <v>646</v>
       </c>
-      <c r="C3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>647</v>
-      </c>
-      <c r="E3" t="s">
-        <v>648</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -7986,45 +8263,45 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>648</v>
+      </c>
+      <c r="B4" t="s">
         <v>649</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
         <v>650</v>
       </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>651</v>
       </c>
-      <c r="E4" t="s">
-        <v>652</v>
-      </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>652</v>
+      </c>
+      <c r="B5" t="s">
         <v>653</v>
-      </c>
-      <c r="B5" t="s">
-        <v>654</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
       <c r="D5" t="s">
+        <v>654</v>
+      </c>
+      <c r="E5" t="s">
         <v>655</v>
       </c>
-      <c r="E5" t="s">
-        <v>656</v>
-      </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -8032,19 +8309,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>656</v>
+      </c>
+      <c r="B6" t="s">
         <v>657</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
         <v>658</v>
       </c>
-      <c r="C6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>659</v>
-      </c>
-      <c r="E6" t="s">
-        <v>660</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
@@ -8055,22 +8332,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>660</v>
+      </c>
+      <c r="B7" t="s">
         <v>661</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" t="s">
         <v>662</v>
       </c>
-      <c r="C7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>663</v>
       </c>
-      <c r="E7" t="s">
-        <v>664</v>
-      </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
         <v>30</v>
@@ -8078,19 +8355,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>664</v>
+      </c>
+      <c r="B8" t="s">
         <v>665</v>
-      </c>
-      <c r="B8" t="s">
-        <v>666</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
       </c>
       <c r="D8" t="s">
+        <v>666</v>
+      </c>
+      <c r="E8" t="s">
         <v>667</v>
-      </c>
-      <c r="E8" t="s">
-        <v>668</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -8101,42 +8378,42 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>668</v>
+      </c>
+      <c r="B9" t="s">
         <v>669</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
         <v>670</v>
       </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>671</v>
       </c>
-      <c r="E9" t="s">
-        <v>672</v>
-      </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>672</v>
+      </c>
+      <c r="B10" t="s">
         <v>673</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
         <v>674</v>
       </c>
-      <c r="C10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>675</v>
-      </c>
-      <c r="E10" t="s">
-        <v>676</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -8147,45 +8424,45 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>676</v>
+      </c>
+      <c r="B11" t="s">
         <v>677</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
         <v>678</v>
       </c>
-      <c r="C11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>679</v>
       </c>
-      <c r="E11" t="s">
-        <v>680</v>
-      </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>680</v>
+      </c>
+      <c r="B12" t="s">
         <v>681</v>
-      </c>
-      <c r="B12" t="s">
-        <v>682</v>
       </c>
       <c r="C12" t="s">
         <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E12" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s">
         <v>30</v>
@@ -8193,42 +8470,42 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>683</v>
+      </c>
+      <c r="B13" t="s">
         <v>684</v>
-      </c>
-      <c r="B13" t="s">
-        <v>685</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>686</v>
+      </c>
+      <c r="B14" t="s">
         <v>687</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>650</v>
+      </c>
+      <c r="E14" t="s">
         <v>688</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" t="s">
-        <v>651</v>
-      </c>
-      <c r="E14" t="s">
-        <v>689</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -8239,22 +8516,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>689</v>
+      </c>
+      <c r="B15" t="s">
         <v>690</v>
-      </c>
-      <c r="B15" t="s">
-        <v>691</v>
       </c>
       <c r="C15" t="s">
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E15" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s">
         <v>30</v>
@@ -8262,22 +8539,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>692</v>
+      </c>
+      <c r="B16" t="s">
         <v>693</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>658</v>
+      </c>
+      <c r="E16" t="s">
         <v>694</v>
       </c>
-      <c r="C16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" t="s">
-        <v>659</v>
-      </c>
-      <c r="E16" t="s">
-        <v>695</v>
-      </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s">
         <v>30</v>
@@ -8285,19 +8562,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>695</v>
+      </c>
+      <c r="B17" t="s">
         <v>696</v>
-      </c>
-      <c r="B17" t="s">
-        <v>697</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E17" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
@@ -8308,19 +8585,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>698</v>
+      </c>
+      <c r="B18" t="s">
         <v>699</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" t="s">
+        <v>666</v>
+      </c>
+      <c r="E18" t="s">
         <v>700</v>
-      </c>
-      <c r="C18" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" t="s">
-        <v>667</v>
-      </c>
-      <c r="E18" t="s">
-        <v>701</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
@@ -8331,22 +8608,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>701</v>
+      </c>
+      <c r="B19" t="s">
         <v>702</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>670</v>
+      </c>
+      <c r="E19" t="s">
         <v>703</v>
       </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" t="s">
-        <v>671</v>
-      </c>
-      <c r="E19" t="s">
-        <v>704</v>
-      </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" t="s">
         <v>24</v>
@@ -8354,19 +8631,19 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>704</v>
+      </c>
+      <c r="B20" t="s">
         <v>705</v>
-      </c>
-      <c r="B20" t="s">
-        <v>706</v>
       </c>
       <c r="C20" t="s">
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E20" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F20" t="s">
         <v>29</v>
@@ -8377,42 +8654,42 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>707</v>
+      </c>
+      <c r="B21" t="s">
         <v>708</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" t="s">
+        <v>678</v>
+      </c>
+      <c r="E21" t="s">
         <v>709</v>
       </c>
-      <c r="C21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" t="s">
-        <v>679</v>
-      </c>
-      <c r="E21" t="s">
-        <v>710</v>
-      </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>710</v>
+      </c>
+      <c r="B22" t="s">
         <v>711</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
+        <v>642</v>
+      </c>
+      <c r="E22" t="s">
         <v>712</v>
-      </c>
-      <c r="C22" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" t="s">
-        <v>643</v>
-      </c>
-      <c r="E22" t="s">
-        <v>713</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
@@ -8423,22 +8700,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>713</v>
+      </c>
+      <c r="B23" t="s">
         <v>714</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>646</v>
+      </c>
+      <c r="E23" t="s">
         <v>715</v>
       </c>
-      <c r="C23" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" t="s">
-        <v>647</v>
-      </c>
-      <c r="E23" t="s">
-        <v>716</v>
-      </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s">
         <v>24</v>
@@ -8446,22 +8723,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>716</v>
+      </c>
+      <c r="B24" t="s">
         <v>717</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" t="s">
+        <v>650</v>
+      </c>
+      <c r="E24" t="s">
         <v>718</v>
       </c>
-      <c r="C24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" t="s">
-        <v>651</v>
-      </c>
-      <c r="E24" t="s">
-        <v>719</v>
-      </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G24" t="s">
         <v>24</v>
@@ -8469,22 +8746,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>719</v>
+      </c>
+      <c r="B25" t="s">
         <v>720</v>
-      </c>
-      <c r="B25" t="s">
-        <v>721</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s">
         <v>24</v>
@@ -8492,19 +8769,19 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>722</v>
+      </c>
+      <c r="B26" t="s">
         <v>723</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" t="s">
+        <v>658</v>
+      </c>
+      <c r="E26" t="s">
         <v>724</v>
-      </c>
-      <c r="C26" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" t="s">
-        <v>659</v>
-      </c>
-      <c r="E26" t="s">
-        <v>725</v>
       </c>
       <c r="F26" t="s">
         <v>29</v>
@@ -8515,22 +8792,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>725</v>
+      </c>
+      <c r="B27" t="s">
         <v>726</v>
-      </c>
-      <c r="B27" t="s">
-        <v>727</v>
       </c>
       <c r="C27" t="s">
         <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E27" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="F27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
@@ -8538,19 +8815,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>728</v>
+      </c>
+      <c r="B28" t="s">
         <v>729</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" t="s">
+        <v>666</v>
+      </c>
+      <c r="E28" t="s">
         <v>730</v>
-      </c>
-      <c r="C28" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" t="s">
-        <v>667</v>
-      </c>
-      <c r="E28" t="s">
-        <v>731</v>
       </c>
       <c r="F28" t="s">
         <v>29</v>
@@ -8561,19 +8838,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>731</v>
+      </c>
+      <c r="B29" t="s">
         <v>732</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
+        <v>670</v>
+      </c>
+      <c r="E29" t="s">
         <v>733</v>
-      </c>
-      <c r="C29" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" t="s">
-        <v>671</v>
-      </c>
-      <c r="E29" t="s">
-        <v>734</v>
       </c>
       <c r="F29" t="s">
         <v>12</v>
@@ -8584,22 +8861,22 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>734</v>
+      </c>
+      <c r="B30" t="s">
         <v>735</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" t="s">
+        <v>674</v>
+      </c>
+      <c r="E30" t="s">
         <v>736</v>
       </c>
-      <c r="C30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" t="s">
-        <v>675</v>
-      </c>
-      <c r="E30" t="s">
-        <v>737</v>
-      </c>
       <c r="F30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G30" t="s">
         <v>24</v>
@@ -8607,22 +8884,22 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>737</v>
+      </c>
+      <c r="B31" t="s">
         <v>738</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" t="s">
+        <v>678</v>
+      </c>
+      <c r="E31" t="s">
         <v>739</v>
       </c>
-      <c r="C31" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" t="s">
-        <v>679</v>
-      </c>
-      <c r="E31" t="s">
-        <v>740</v>
-      </c>
       <c r="F31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
@@ -8630,42 +8907,42 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>740</v>
+      </c>
+      <c r="B32" t="s">
         <v>741</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" t="s">
+        <v>642</v>
+      </c>
+      <c r="E32" t="s">
         <v>742</v>
       </c>
-      <c r="C32" t="s">
-        <v>43</v>
-      </c>
-      <c r="D32" t="s">
-        <v>643</v>
-      </c>
-      <c r="E32" t="s">
-        <v>743</v>
-      </c>
       <c r="F32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>743</v>
+      </c>
+      <c r="B33" t="s">
         <v>744</v>
-      </c>
-      <c r="B33" t="s">
-        <v>745</v>
       </c>
       <c r="C33" t="s">
         <v>21</v>
       </c>
       <c r="D33" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E33" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F33" t="s">
         <v>12</v>
@@ -8676,19 +8953,19 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>746</v>
+      </c>
+      <c r="B34" t="s">
         <v>747</v>
-      </c>
-      <c r="B34" t="s">
-        <v>748</v>
       </c>
       <c r="C34" t="s">
         <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E34" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
@@ -8699,22 +8976,22 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>749</v>
+      </c>
+      <c r="B35" t="s">
         <v>750</v>
-      </c>
-      <c r="B35" t="s">
-        <v>751</v>
       </c>
       <c r="C35" t="s">
         <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E35" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -8722,22 +8999,22 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>752</v>
+      </c>
+      <c r="B36" t="s">
         <v>753</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" t="s">
+        <v>658</v>
+      </c>
+      <c r="E36" t="s">
         <v>754</v>
       </c>
-      <c r="C36" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" t="s">
-        <v>659</v>
-      </c>
-      <c r="E36" t="s">
-        <v>755</v>
-      </c>
       <c r="F36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G36" t="s">
         <v>30</v>
@@ -8745,19 +9022,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>755</v>
+      </c>
+      <c r="B37" t="s">
         <v>756</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" t="s">
+        <v>662</v>
+      </c>
+      <c r="E37" t="s">
         <v>757</v>
-      </c>
-      <c r="C37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D37" t="s">
-        <v>663</v>
-      </c>
-      <c r="E37" t="s">
-        <v>758</v>
       </c>
       <c r="F37" t="s">
         <v>12</v>
@@ -8768,22 +9045,22 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>758</v>
+      </c>
+      <c r="B38" t="s">
         <v>759</v>
-      </c>
-      <c r="B38" t="s">
-        <v>760</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E38" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G38" t="s">
         <v>24</v>
@@ -8791,22 +9068,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>761</v>
+      </c>
+      <c r="B39" t="s">
         <v>762</v>
-      </c>
-      <c r="B39" t="s">
-        <v>763</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
       </c>
       <c r="D39" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E39" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s">
         <v>30</v>
@@ -8814,22 +9091,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>764</v>
+      </c>
+      <c r="B40" t="s">
         <v>765</v>
-      </c>
-      <c r="B40" t="s">
-        <v>766</v>
       </c>
       <c r="C40" t="s">
         <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E40" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G40" t="s">
         <v>24</v>
@@ -8837,42 +9114,42 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>767</v>
+      </c>
+      <c r="B41" t="s">
         <v>768</v>
-      </c>
-      <c r="B41" t="s">
-        <v>769</v>
       </c>
       <c r="C41" t="s">
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E41" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F41" t="s">
         <v>12</v>
       </c>
       <c r="G41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>770</v>
+      </c>
+      <c r="B42" t="s">
         <v>771</v>
-      </c>
-      <c r="B42" t="s">
-        <v>772</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
       </c>
       <c r="D42" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E42" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F42" t="s">
         <v>12</v>
@@ -8883,45 +9160,45 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>773</v>
+      </c>
+      <c r="B43" t="s">
         <v>774</v>
-      </c>
-      <c r="B43" t="s">
-        <v>775</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
       </c>
       <c r="D43" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E43" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F43" t="s">
         <v>29</v>
       </c>
       <c r="G43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>776</v>
+      </c>
+      <c r="B44" t="s">
         <v>777</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" t="s">
+        <v>650</v>
+      </c>
+      <c r="E44" t="s">
         <v>778</v>
       </c>
-      <c r="C44" t="s">
-        <v>43</v>
-      </c>
-      <c r="D44" t="s">
-        <v>651</v>
-      </c>
-      <c r="E44" t="s">
-        <v>779</v>
-      </c>
       <c r="F44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s">
         <v>30</v>
@@ -8929,19 +9206,19 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>779</v>
+      </c>
+      <c r="B45" t="s">
         <v>780</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D45" t="s">
+        <v>654</v>
+      </c>
+      <c r="E45" t="s">
         <v>781</v>
-      </c>
-      <c r="C45" t="s">
-        <v>43</v>
-      </c>
-      <c r="D45" t="s">
-        <v>655</v>
-      </c>
-      <c r="E45" t="s">
-        <v>782</v>
       </c>
       <c r="F45" t="s">
         <v>29</v>
@@ -8952,19 +9229,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>782</v>
+      </c>
+      <c r="B46" t="s">
         <v>783</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
+        <v>59</v>
+      </c>
+      <c r="D46" t="s">
+        <v>658</v>
+      </c>
+      <c r="E46" t="s">
         <v>784</v>
-      </c>
-      <c r="C46" t="s">
-        <v>60</v>
-      </c>
-      <c r="D46" t="s">
-        <v>659</v>
-      </c>
-      <c r="E46" t="s">
-        <v>785</v>
       </c>
       <c r="F46" t="s">
         <v>29</v>
@@ -8975,19 +9252,19 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>785</v>
+      </c>
+      <c r="B47" t="s">
         <v>786</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" t="s">
+        <v>662</v>
+      </c>
+      <c r="E47" t="s">
         <v>787</v>
-      </c>
-      <c r="C47" t="s">
-        <v>60</v>
-      </c>
-      <c r="D47" t="s">
-        <v>663</v>
-      </c>
-      <c r="E47" t="s">
-        <v>788</v>
       </c>
       <c r="F47" t="s">
         <v>29</v>
@@ -8998,22 +9275,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>788</v>
+      </c>
+      <c r="B48" t="s">
         <v>789</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" t="s">
+        <v>666</v>
+      </c>
+      <c r="E48" t="s">
         <v>790</v>
       </c>
-      <c r="C48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D48" t="s">
-        <v>667</v>
-      </c>
-      <c r="E48" t="s">
-        <v>791</v>
-      </c>
       <c r="F48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G48" t="s">
         <v>24</v>
@@ -9021,19 +9298,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>791</v>
+      </c>
+      <c r="B49" t="s">
         <v>792</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" t="s">
+        <v>670</v>
+      </c>
+      <c r="E49" t="s">
         <v>793</v>
-      </c>
-      <c r="C49" t="s">
-        <v>60</v>
-      </c>
-      <c r="D49" t="s">
-        <v>671</v>
-      </c>
-      <c r="E49" t="s">
-        <v>794</v>
       </c>
       <c r="F49" t="s">
         <v>12</v>
@@ -9044,45 +9321,45 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>794</v>
+      </c>
+      <c r="B50" t="s">
         <v>795</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
+        <v>42</v>
+      </c>
+      <c r="D50" t="s">
+        <v>674</v>
+      </c>
+      <c r="E50" t="s">
         <v>796</v>
       </c>
-      <c r="C50" t="s">
-        <v>43</v>
-      </c>
-      <c r="D50" t="s">
-        <v>675</v>
-      </c>
-      <c r="E50" t="s">
-        <v>797</v>
-      </c>
       <c r="F50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>797</v>
+      </c>
+      <c r="B51" t="s">
         <v>798</v>
-      </c>
-      <c r="B51" t="s">
-        <v>799</v>
       </c>
       <c r="C51" t="s">
         <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E51" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G51" t="s">
         <v>24</v>
@@ -9090,19 +9367,19 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>800</v>
+      </c>
+      <c r="B52" t="s">
         <v>801</v>
-      </c>
-      <c r="B52" t="s">
-        <v>802</v>
       </c>
       <c r="C52" t="s">
         <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E52" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F52" t="s">
         <v>12</v>
@@ -9113,42 +9390,42 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>803</v>
+      </c>
+      <c r="B53" t="s">
         <v>804</v>
-      </c>
-      <c r="B53" t="s">
-        <v>805</v>
       </c>
       <c r="C53" t="s">
         <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E53" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F53" t="s">
         <v>29</v>
       </c>
       <c r="G53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>806</v>
+      </c>
+      <c r="B54" t="s">
         <v>807</v>
-      </c>
-      <c r="B54" t="s">
-        <v>808</v>
       </c>
       <c r="C54" t="s">
         <v>9</v>
       </c>
       <c r="D54" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E54" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F54" t="s">
         <v>12</v>
@@ -9159,19 +9436,19 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>809</v>
+      </c>
+      <c r="B55" t="s">
         <v>810</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" t="s">
+        <v>654</v>
+      </c>
+      <c r="E55" t="s">
         <v>811</v>
-      </c>
-      <c r="C55" t="s">
-        <v>70</v>
-      </c>
-      <c r="D55" t="s">
-        <v>655</v>
-      </c>
-      <c r="E55" t="s">
-        <v>812</v>
       </c>
       <c r="F55" t="s">
         <v>29</v>
@@ -9182,19 +9459,19 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>812</v>
+      </c>
+      <c r="B56" t="s">
         <v>813</v>
-      </c>
-      <c r="B56" t="s">
-        <v>814</v>
       </c>
       <c r="C56" t="s">
         <v>16</v>
       </c>
       <c r="D56" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E56" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F56" t="s">
         <v>29</v>
@@ -9205,42 +9482,42 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>815</v>
+      </c>
+      <c r="B57" t="s">
         <v>816</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
+        <v>59</v>
+      </c>
+      <c r="D57" t="s">
+        <v>662</v>
+      </c>
+      <c r="E57" t="s">
         <v>817</v>
       </c>
-      <c r="C57" t="s">
-        <v>60</v>
-      </c>
-      <c r="D57" t="s">
-        <v>663</v>
-      </c>
-      <c r="E57" t="s">
-        <v>818</v>
-      </c>
       <c r="F57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>818</v>
+      </c>
+      <c r="B58" t="s">
         <v>819</v>
-      </c>
-      <c r="B58" t="s">
-        <v>820</v>
       </c>
       <c r="C58" t="s">
         <v>16</v>
       </c>
       <c r="D58" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E58" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F58" t="s">
         <v>12</v>
@@ -9251,68 +9528,68 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>821</v>
+      </c>
+      <c r="B59" t="s">
         <v>822</v>
-      </c>
-      <c r="B59" t="s">
-        <v>823</v>
       </c>
       <c r="C59" t="s">
         <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E59" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>824</v>
+      </c>
+      <c r="B60" t="s">
         <v>825</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
+        <v>42</v>
+      </c>
+      <c r="D60" t="s">
+        <v>674</v>
+      </c>
+      <c r="E60" t="s">
         <v>826</v>
-      </c>
-      <c r="C60" t="s">
-        <v>43</v>
-      </c>
-      <c r="D60" t="s">
-        <v>675</v>
-      </c>
-      <c r="E60" t="s">
-        <v>827</v>
       </c>
       <c r="F60" t="s">
         <v>12</v>
       </c>
       <c r="G60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>827</v>
+      </c>
+      <c r="B61" t="s">
         <v>828</v>
-      </c>
-      <c r="B61" t="s">
-        <v>829</v>
       </c>
       <c r="C61" t="s">
         <v>9</v>
       </c>
       <c r="D61" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E61" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="F61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G61" t="s">
         <v>24</v>
@@ -9320,42 +9597,42 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>830</v>
+      </c>
+      <c r="B62" t="s">
         <v>831</v>
-      </c>
-      <c r="B62" t="s">
-        <v>832</v>
       </c>
       <c r="C62" t="s">
         <v>21</v>
       </c>
       <c r="D62" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E62" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F62" t="s">
         <v>29</v>
       </c>
       <c r="G62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>833</v>
+      </c>
+      <c r="B63" t="s">
         <v>834</v>
-      </c>
-      <c r="B63" t="s">
-        <v>835</v>
       </c>
       <c r="C63" t="s">
         <v>21</v>
       </c>
       <c r="D63" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E63" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
@@ -9366,19 +9643,19 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>836</v>
+      </c>
+      <c r="B64" t="s">
         <v>837</v>
-      </c>
-      <c r="B64" t="s">
-        <v>838</v>
       </c>
       <c r="C64" t="s">
         <v>16</v>
       </c>
       <c r="D64" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E64" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F64" t="s">
         <v>12</v>
@@ -9389,19 +9666,19 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>839</v>
+      </c>
+      <c r="B65" t="s">
         <v>840</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" t="s">
+        <v>654</v>
+      </c>
+      <c r="E65" t="s">
         <v>841</v>
-      </c>
-      <c r="C65" t="s">
-        <v>70</v>
-      </c>
-      <c r="D65" t="s">
-        <v>655</v>
-      </c>
-      <c r="E65" t="s">
-        <v>842</v>
       </c>
       <c r="F65" t="s">
         <v>12</v>
@@ -9412,19 +9689,19 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>842</v>
+      </c>
+      <c r="B66" t="s">
         <v>843</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
+        <v>69</v>
+      </c>
+      <c r="D66" t="s">
+        <v>658</v>
+      </c>
+      <c r="E66" t="s">
         <v>844</v>
-      </c>
-      <c r="C66" t="s">
-        <v>70</v>
-      </c>
-      <c r="D66" t="s">
-        <v>659</v>
-      </c>
-      <c r="E66" t="s">
-        <v>845</v>
       </c>
       <c r="F66" t="s">
         <v>12</v>
@@ -9435,22 +9712,22 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>845</v>
+      </c>
+      <c r="B67" t="s">
         <v>846</v>
-      </c>
-      <c r="B67" t="s">
-        <v>847</v>
       </c>
       <c r="C67" t="s">
         <v>16</v>
       </c>
       <c r="D67" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E67" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G67" t="s">
         <v>30</v>
@@ -9458,45 +9735,45 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>848</v>
+      </c>
+      <c r="B68" t="s">
         <v>849</v>
-      </c>
-      <c r="B68" t="s">
-        <v>850</v>
       </c>
       <c r="C68" t="s">
         <v>21</v>
       </c>
       <c r="D68" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E68" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>851</v>
+      </c>
+      <c r="B69" t="s">
         <v>852</v>
-      </c>
-      <c r="B69" t="s">
-        <v>853</v>
       </c>
       <c r="C69" t="s">
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E69" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
@@ -9504,22 +9781,22 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>854</v>
+      </c>
+      <c r="B70" t="s">
         <v>855</v>
-      </c>
-      <c r="B70" t="s">
-        <v>856</v>
       </c>
       <c r="C70" t="s">
         <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E70" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G70" t="s">
         <v>30</v>
@@ -9527,22 +9804,22 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>857</v>
+      </c>
+      <c r="B71" t="s">
         <v>858</v>
-      </c>
-      <c r="B71" t="s">
-        <v>859</v>
       </c>
       <c r="C71" t="s">
         <v>16</v>
       </c>
       <c r="D71" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E71" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F71" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G71" t="s">
         <v>30</v>
@@ -9550,19 +9827,19 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>860</v>
+      </c>
+      <c r="B72" t="s">
         <v>861</v>
-      </c>
-      <c r="B72" t="s">
-        <v>862</v>
       </c>
       <c r="C72" t="s">
         <v>16</v>
       </c>
       <c r="D72" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E72" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F72" t="s">
         <v>12</v>
@@ -9573,19 +9850,19 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>863</v>
+      </c>
+      <c r="B73" t="s">
         <v>864</v>
-      </c>
-      <c r="B73" t="s">
-        <v>865</v>
       </c>
       <c r="C73" t="s">
         <v>16</v>
       </c>
       <c r="D73" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E73" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F73" t="s">
         <v>29</v>
@@ -9596,65 +9873,65 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>866</v>
+      </c>
+      <c r="B74" t="s">
         <v>867</v>
-      </c>
-      <c r="B74" t="s">
-        <v>868</v>
       </c>
       <c r="C74" t="s">
         <v>9</v>
       </c>
       <c r="D74" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E74" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F74" t="s">
         <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>869</v>
+      </c>
+      <c r="B75" t="s">
         <v>870</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
+        <v>69</v>
+      </c>
+      <c r="D75" t="s">
+        <v>654</v>
+      </c>
+      <c r="E75" t="s">
         <v>871</v>
       </c>
-      <c r="C75" t="s">
-        <v>70</v>
-      </c>
-      <c r="D75" t="s">
-        <v>655</v>
-      </c>
-      <c r="E75" t="s">
-        <v>872</v>
-      </c>
       <c r="F75" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G75" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>872</v>
+      </c>
+      <c r="B76" t="s">
         <v>873</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
+        <v>59</v>
+      </c>
+      <c r="D76" t="s">
+        <v>658</v>
+      </c>
+      <c r="E76" t="s">
         <v>874</v>
-      </c>
-      <c r="C76" t="s">
-        <v>60</v>
-      </c>
-      <c r="D76" t="s">
-        <v>659</v>
-      </c>
-      <c r="E76" t="s">
-        <v>875</v>
       </c>
       <c r="F76" t="s">
         <v>29</v>
@@ -9665,22 +9942,22 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>875</v>
+      </c>
+      <c r="B77" t="s">
         <v>876</v>
-      </c>
-      <c r="B77" t="s">
-        <v>877</v>
       </c>
       <c r="C77" t="s">
         <v>21</v>
       </c>
       <c r="D77" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E77" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G77" t="s">
         <v>30</v>
@@ -9688,19 +9965,19 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>878</v>
+      </c>
+      <c r="B78" t="s">
         <v>879</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
+        <v>69</v>
+      </c>
+      <c r="D78" t="s">
+        <v>666</v>
+      </c>
+      <c r="E78" t="s">
         <v>880</v>
-      </c>
-      <c r="C78" t="s">
-        <v>70</v>
-      </c>
-      <c r="D78" t="s">
-        <v>667</v>
-      </c>
-      <c r="E78" t="s">
-        <v>881</v>
       </c>
       <c r="F78" t="s">
         <v>12</v>
@@ -9711,19 +9988,19 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>881</v>
+      </c>
+      <c r="B79" t="s">
         <v>882</v>
-      </c>
-      <c r="B79" t="s">
-        <v>883</v>
       </c>
       <c r="C79" t="s">
         <v>21</v>
       </c>
       <c r="D79" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E79" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F79" t="s">
         <v>29</v>
@@ -9734,22 +10011,22 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>884</v>
+      </c>
+      <c r="B80" t="s">
         <v>885</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
+        <v>42</v>
+      </c>
+      <c r="D80" t="s">
+        <v>674</v>
+      </c>
+      <c r="E80" t="s">
         <v>886</v>
       </c>
-      <c r="C80" t="s">
-        <v>43</v>
-      </c>
-      <c r="D80" t="s">
-        <v>675</v>
-      </c>
-      <c r="E80" t="s">
-        <v>887</v>
-      </c>
       <c r="F80" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G80" t="s">
         <v>30</v>
@@ -9757,42 +10034,42 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>887</v>
+      </c>
+      <c r="B81" t="s">
         <v>888</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
+        <v>69</v>
+      </c>
+      <c r="D81" t="s">
+        <v>678</v>
+      </c>
+      <c r="E81" t="s">
         <v>889</v>
       </c>
-      <c r="C81" t="s">
-        <v>70</v>
-      </c>
-      <c r="D81" t="s">
-        <v>679</v>
-      </c>
-      <c r="E81" t="s">
-        <v>890</v>
-      </c>
       <c r="F81" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G81" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>890</v>
+      </c>
+      <c r="B82" t="s">
         <v>891</v>
-      </c>
-      <c r="B82" t="s">
-        <v>892</v>
       </c>
       <c r="C82" t="s">
         <v>16</v>
       </c>
       <c r="D82" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E82" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F82" t="s">
         <v>12</v>
@@ -9803,19 +10080,19 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>893</v>
+      </c>
+      <c r="B83" t="s">
         <v>894</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
+        <v>59</v>
+      </c>
+      <c r="D83" t="s">
+        <v>646</v>
+      </c>
+      <c r="E83" t="s">
         <v>895</v>
-      </c>
-      <c r="C83" t="s">
-        <v>60</v>
-      </c>
-      <c r="D83" t="s">
-        <v>647</v>
-      </c>
-      <c r="E83" t="s">
-        <v>896</v>
       </c>
       <c r="F83" t="s">
         <v>29</v>
@@ -9826,19 +10103,19 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>896</v>
+      </c>
+      <c r="B84" t="s">
         <v>897</v>
-      </c>
-      <c r="B84" t="s">
-        <v>898</v>
       </c>
       <c r="C84" t="s">
         <v>16</v>
       </c>
       <c r="D84" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E84" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F84" t="s">
         <v>29</v>
@@ -9849,45 +10126,45 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>899</v>
+      </c>
+      <c r="B85" t="s">
         <v>900</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
+        <v>59</v>
+      </c>
+      <c r="D85" t="s">
+        <v>654</v>
+      </c>
+      <c r="E85" t="s">
         <v>901</v>
       </c>
-      <c r="C85" t="s">
-        <v>60</v>
-      </c>
-      <c r="D85" t="s">
-        <v>655</v>
-      </c>
-      <c r="E85" t="s">
-        <v>902</v>
-      </c>
       <c r="F85" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G85" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>902</v>
+      </c>
+      <c r="B86" t="s">
         <v>903</v>
-      </c>
-      <c r="B86" t="s">
-        <v>904</v>
       </c>
       <c r="C86" t="s">
         <v>16</v>
       </c>
       <c r="D86" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E86" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F86" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G86" t="s">
         <v>24</v>
@@ -9895,42 +10172,42 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>905</v>
+      </c>
+      <c r="B87" t="s">
         <v>906</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
+        <v>42</v>
+      </c>
+      <c r="D87" t="s">
+        <v>662</v>
+      </c>
+      <c r="E87" t="s">
         <v>907</v>
       </c>
-      <c r="C87" t="s">
-        <v>43</v>
-      </c>
-      <c r="D87" t="s">
-        <v>663</v>
-      </c>
-      <c r="E87" t="s">
-        <v>908</v>
-      </c>
       <c r="F87" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G87" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>908</v>
+      </c>
+      <c r="B88" t="s">
         <v>909</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
+        <v>59</v>
+      </c>
+      <c r="D88" t="s">
+        <v>666</v>
+      </c>
+      <c r="E88" t="s">
         <v>910</v>
-      </c>
-      <c r="C88" t="s">
-        <v>60</v>
-      </c>
-      <c r="D88" t="s">
-        <v>667</v>
-      </c>
-      <c r="E88" t="s">
-        <v>911</v>
       </c>
       <c r="F88" t="s">
         <v>29</v>
@@ -9941,45 +10218,45 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>911</v>
+      </c>
+      <c r="B89" t="s">
         <v>912</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
+        <v>59</v>
+      </c>
+      <c r="D89" t="s">
+        <v>670</v>
+      </c>
+      <c r="E89" t="s">
         <v>913</v>
       </c>
-      <c r="C89" t="s">
-        <v>60</v>
-      </c>
-      <c r="D89" t="s">
-        <v>671</v>
-      </c>
-      <c r="E89" t="s">
-        <v>914</v>
-      </c>
       <c r="F89" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>914</v>
+      </c>
+      <c r="B90" t="s">
         <v>915</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
+        <v>59</v>
+      </c>
+      <c r="D90" t="s">
+        <v>674</v>
+      </c>
+      <c r="E90" t="s">
         <v>916</v>
       </c>
-      <c r="C90" t="s">
-        <v>60</v>
-      </c>
-      <c r="D90" t="s">
-        <v>675</v>
-      </c>
-      <c r="E90" t="s">
-        <v>917</v>
-      </c>
       <c r="F90" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G90" t="s">
         <v>24</v>
@@ -9987,45 +10264,45 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>917</v>
+      </c>
+      <c r="B91" t="s">
         <v>918</v>
-      </c>
-      <c r="B91" t="s">
-        <v>919</v>
       </c>
       <c r="C91" t="s">
         <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E91" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F91" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G91" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>920</v>
+      </c>
+      <c r="B92" t="s">
         <v>921</v>
-      </c>
-      <c r="B92" t="s">
-        <v>922</v>
       </c>
       <c r="C92" t="s">
         <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E92" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F92" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G92" t="s">
         <v>13</v>
@@ -10033,45 +10310,45 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>923</v>
+      </c>
+      <c r="B93" t="s">
         <v>924</v>
-      </c>
-      <c r="B93" t="s">
-        <v>925</v>
       </c>
       <c r="C93" t="s">
         <v>9</v>
       </c>
       <c r="D93" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E93" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="F93" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>926</v>
+      </c>
+      <c r="B94" t="s">
         <v>927</v>
-      </c>
-      <c r="B94" t="s">
-        <v>928</v>
       </c>
       <c r="C94" t="s">
         <v>16</v>
       </c>
       <c r="D94" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E94" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F94" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G94" t="s">
         <v>24</v>
@@ -10079,19 +10356,19 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>929</v>
+      </c>
+      <c r="B95" t="s">
         <v>930</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
+        <v>59</v>
+      </c>
+      <c r="D95" t="s">
+        <v>654</v>
+      </c>
+      <c r="E95" t="s">
         <v>931</v>
-      </c>
-      <c r="C95" t="s">
-        <v>60</v>
-      </c>
-      <c r="D95" t="s">
-        <v>655</v>
-      </c>
-      <c r="E95" t="s">
-        <v>932</v>
       </c>
       <c r="F95" t="s">
         <v>12</v>
@@ -10102,22 +10379,22 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
+        <v>932</v>
+      </c>
+      <c r="B96" t="s">
         <v>933</v>
-      </c>
-      <c r="B96" t="s">
-        <v>934</v>
       </c>
       <c r="C96" t="s">
         <v>21</v>
       </c>
       <c r="D96" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E96" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F96" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G96" t="s">
         <v>13</v>
@@ -10125,45 +10402,45 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>935</v>
+      </c>
+      <c r="B97" t="s">
         <v>936</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
+        <v>69</v>
+      </c>
+      <c r="D97" t="s">
+        <v>662</v>
+      </c>
+      <c r="E97" t="s">
         <v>937</v>
       </c>
-      <c r="C97" t="s">
-        <v>70</v>
-      </c>
-      <c r="D97" t="s">
-        <v>663</v>
-      </c>
-      <c r="E97" t="s">
-        <v>938</v>
-      </c>
       <c r="F97" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G97" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>938</v>
+      </c>
+      <c r="B98" t="s">
         <v>939</v>
-      </c>
-      <c r="B98" t="s">
-        <v>940</v>
       </c>
       <c r="C98" t="s">
         <v>21</v>
       </c>
       <c r="D98" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E98" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F98" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G98" t="s">
         <v>13</v>
@@ -10171,19 +10448,19 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>941</v>
+      </c>
+      <c r="B99" t="s">
         <v>942</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
+        <v>42</v>
+      </c>
+      <c r="D99" t="s">
+        <v>670</v>
+      </c>
+      <c r="E99" t="s">
         <v>943</v>
-      </c>
-      <c r="C99" t="s">
-        <v>43</v>
-      </c>
-      <c r="D99" t="s">
-        <v>671</v>
-      </c>
-      <c r="E99" t="s">
-        <v>944</v>
       </c>
       <c r="F99" t="s">
         <v>29</v>
@@ -10194,48 +10471,48 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>944</v>
+      </c>
+      <c r="B100" t="s">
         <v>945</v>
-      </c>
-      <c r="B100" t="s">
-        <v>946</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
       </c>
       <c r="D100" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E100" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F100" t="s">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>947</v>
+      </c>
+      <c r="B101" t="s">
         <v>948</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
+        <v>42</v>
+      </c>
+      <c r="D101" t="s">
+        <v>678</v>
+      </c>
+      <c r="E101" t="s">
         <v>949</v>
-      </c>
-      <c r="C101" t="s">
-        <v>43</v>
-      </c>
-      <c r="D101" t="s">
-        <v>679</v>
-      </c>
-      <c r="E101" t="s">
-        <v>950</v>
       </c>
       <c r="F101" t="s">
         <v>29</v>
       </c>
       <c r="G101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/games_database.xlsx
+++ b/games_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\azree\OneDrive\Desktop\Github Repro\Capstone\JustAnotherDiscordRichPresenceApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEC5260-D4C4-4DB7-BDE4-1A37A0C210F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFA44C3-8297-42B1-B260-96E45C5AD714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OG Xbox" sheetId="7" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="PS5" sheetId="3" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PS1'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PS2'!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5144" uniqueCount="1853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5282" uniqueCount="1917">
   <si>
     <t>Game Title</t>
   </si>
@@ -5590,6 +5591,198 @@
   </si>
   <si>
     <t>Playing Metal Slug Anthology</t>
+  </si>
+  <si>
+    <t>Final Fantasy VII</t>
+  </si>
+  <si>
+    <t>Playing Final Fantasy VII</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn1.gstatic.com/images?q=tbn:ANd9GcTpTUSb1Tq9LmPnFILxUCIVVhE8Di_qUoEeYSjlBUiyQhuM-jnN0BZv_EnIGUMx8r4i6Am_</t>
+  </si>
+  <si>
+    <t>Final Fantasy VII Cover</t>
+  </si>
+  <si>
+    <t>Final Fantasy VIII</t>
+  </si>
+  <si>
+    <t>Playing Final Fantasy VIII</t>
+  </si>
+  <si>
+    <t>Final Fantasy VIII Cover</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/fr/6/62/Final_Fantasy_VIII_Logo.png</t>
+  </si>
+  <si>
+    <t>Final Fantasy Tactics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Legend Of Dragoon </t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn2.gstatic.com/images?q=tbn:ANd9GcRPuP4ianbiH0cLRtPqtkarDS7ENIodZdIxN5bv7lSRc0YUT6RWR7p1KE2zpe7RPZXlQPjI6A</t>
+  </si>
+  <si>
+    <t>Playing The Legend Of Dragoon</t>
+  </si>
+  <si>
+    <t>Air Combat</t>
+  </si>
+  <si>
+    <t>Ace Combat 2</t>
+  </si>
+  <si>
+    <t>Ace Combat 3: Electrosphere</t>
+  </si>
+  <si>
+    <t>The Adventure of Little Ralph</t>
+  </si>
+  <si>
+    <t>The Adventures of Lomax</t>
+  </si>
+  <si>
+    <t>Agent Armstrong</t>
+  </si>
+  <si>
+    <t>Agile Warrior F-111X</t>
+  </si>
+  <si>
+    <t>Aironauts</t>
+  </si>
+  <si>
+    <t>Ape Escape</t>
+  </si>
+  <si>
+    <t>Alundra</t>
+  </si>
+  <si>
+    <t>Akuji the Heartless</t>
+  </si>
+  <si>
+    <t>Alien Trilogy</t>
+  </si>
+  <si>
+    <t>Arc the Lad II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arc the Lad </t>
+  </si>
+  <si>
+    <t>Alice in Cyberland</t>
+  </si>
+  <si>
+    <t>Alien: Resurrection</t>
+  </si>
+  <si>
+    <t>ALIVE</t>
+  </si>
+  <si>
+    <t>Alone in the Dark: One-Eyed Jack's Revenge</t>
+  </si>
+  <si>
+    <t>Alone in the Dark: The New Nightmare</t>
+  </si>
+  <si>
+    <t>Alundra 2: A New Legend Begins</t>
+  </si>
+  <si>
+    <t>Amerzone</t>
+  </si>
+  <si>
+    <t>Arc the Lad III</t>
+  </si>
+  <si>
+    <t>Final Fantasy IX</t>
+  </si>
+  <si>
+    <t>Vagrant Story</t>
+  </si>
+  <si>
+    <t>WipEout XL</t>
+  </si>
+  <si>
+    <t>Gran Turismo</t>
+  </si>
+  <si>
+    <t>CTR: Crash Team Racing</t>
+  </si>
+  <si>
+    <t>Crash Bandicoot: Warped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Street Fighter Alpha: Warriors' Dreams	</t>
+  </si>
+  <si>
+    <t>Gran Turismo 2</t>
+  </si>
+  <si>
+    <t>Silent Hill</t>
+  </si>
+  <si>
+    <t>WipEout 3</t>
+  </si>
+  <si>
+    <t>Chrono Cross</t>
+  </si>
+  <si>
+    <t>Soul Blade</t>
+  </si>
+  <si>
+    <t>Xenogears</t>
+  </si>
+  <si>
+    <t>R4: Ridge Racer Type 4</t>
+  </si>
+  <si>
+    <t>Resident Evil 3: Nemesis</t>
+  </si>
+  <si>
+    <t>Lunar: Silver Star Story - Complete</t>
+  </si>
+  <si>
+    <t>Parasite Eve</t>
+  </si>
+  <si>
+    <t>Valkyrie Profile</t>
+  </si>
+  <si>
+    <t>Dino Crisis</t>
+  </si>
+  <si>
+    <t>Final Fantasy Anthology</t>
+  </si>
+  <si>
+    <t>Castlevania: Symphony of the Night</t>
+  </si>
+  <si>
+    <t>Armored Core</t>
+  </si>
+  <si>
+    <t>Armored Core: Project Phantasma</t>
+  </si>
+  <si>
+    <t>Armored Core: Master of Arena</t>
+  </si>
+  <si>
+    <t>Ark of Time</t>
+  </si>
+  <si>
+    <t>Akuji: The Heartless</t>
+  </si>
+  <si>
+    <t>Area 51</t>
+  </si>
+  <si>
+    <t>Armorines: Project S.W.A.R.M.</t>
+  </si>
+  <si>
+    <t>Arthur to Astaroth no Nazomakaimura: Incredible Toons</t>
+  </si>
+  <si>
+    <t>Assault: Retribution</t>
   </si>
 </sst>
 </file>
@@ -6098,15 +6291,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFEDB219-5142-4DD7-A4D0-88AB6C946699}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6133,7 +6326,547 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B2" t="s">
+        <v>973</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B3" t="s">
+        <v>973</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B4" t="s">
+        <v>973</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B5" t="s">
+        <v>973</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B6" t="s">
+        <v>973</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B7" t="s">
+        <v>973</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B8" t="s">
+        <v>973</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B9" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B10" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B11" t="s">
+        <v>973</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B12" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B13" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B14" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B15" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B16" t="s">
+        <v>973</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B17" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B18" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B19" t="s">
+        <v>973</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B20" t="s">
+        <v>973</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B21" t="s">
+        <v>973</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B22" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B23" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B24" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B25" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B26" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B27" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B28" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B29" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B30" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B31" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B32" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B33" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B34" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B35" t="s">
+        <v>973</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1856</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="G36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1859</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="G37" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B38" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B39" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B40" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B41" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B42" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B43" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B44" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B45" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B46" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B47" t="s">
+        <v>973</v>
+      </c>
+      <c r="C47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B48" t="s">
+        <v>973</v>
+      </c>
+      <c r="C48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B50" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B51" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B52" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B53" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B54" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>1916</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:G4" xr:uid="{FFEDB219-5142-4DD7-A4D0-88AB6C946699}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G54">
+      <sortCondition ref="A1:A4"/>
+    </sortState>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G4">
+    <sortCondition ref="A1:A4"/>
+  </sortState>
+  <hyperlinks>
+    <hyperlink ref="D36" r:id="rId1" xr:uid="{01C1AC95-F9E7-439E-86B6-933E3D1C53E1}"/>
+    <hyperlink ref="D37" r:id="rId2" xr:uid="{972522BD-2206-4187-B572-9BCC745D9D2D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/games_database.xlsx
+++ b/games_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\azree\OneDrive\Desktop\Github Repro\Capstone\JustAnotherDiscordRichPresenceApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFA44C3-8297-42B1-B260-96E45C5AD714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91447F69-79AE-4254-A753-321118D09B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5282" uniqueCount="1917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5289" uniqueCount="1924">
   <si>
     <t>Game Title</t>
   </si>
@@ -5783,6 +5783,27 @@
   </si>
   <si>
     <t>Assault: Retribution</t>
+  </si>
+  <si>
+    <t>King's Field</t>
+  </si>
+  <si>
+    <t>King's Field II</t>
+  </si>
+  <si>
+    <t>King's Field III</t>
+  </si>
+  <si>
+    <t>Shadow Tower</t>
+  </si>
+  <si>
+    <t>Echo Night</t>
+  </si>
+  <si>
+    <t>Echo Night 2: The Lord of Nightmares</t>
+  </si>
+  <si>
+    <t>Spriggan: Lunar Verse</t>
   </si>
 </sst>
 </file>
@@ -6291,7 +6312,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFEDB219-5142-4DD7-A4D0-88AB6C946699}">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -6852,6 +6873,41 @@
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>1916</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>1923</v>
       </c>
     </row>
   </sheetData>
